--- a/code/测试集.xlsx
+++ b/code/测试集.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\rag_project\code\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF1D87AE-6F18-4773-896F-6B9DEB83D769}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9EBCE832-4838-4DCB-B419-5035A57A649E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -106,10 +106,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t xml:space="preserve"> "it is simple to develop methods for preserving privacy using our proposed framework by transmitting only de-identified queries and structured knowledge instead of full responses"</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>SETR模型在训练时使用了多少个GPU？具体的训练时间是多少小时？</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -134,30 +130,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t xml:space="preserve"> Think&amp; Cite框架中的Self-Guided Monte Carlo Tree Search (SG-MCTS)如何工作？请描述其核心机制。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>SG-MCTS利用LLMs的自反思能力来推理MCTS的中间状态，以指导树扩展过程。它将归因文本生成表述为与搜索集成的多步推理问题，通过迭代的思考-表达-引用生成范式，让模型能够对主题进行深思熟虑并输出可靠的内容和准确的引用。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>论文 2025.acl-long.490.pdf（Think&amp; Cite），第1页</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>DragonBall数据集包含多少个问题？涵盖哪些语言和领域？</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>DragonBall数据集总共包含6,711个问题，涵盖中文和英文两种语言，覆盖金融、法律和医疗三个关键领域。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>论文 2025.acl-long.418.pdf（DragonBall），第4页</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>比较MEMERAG和DragonBall两个基准的异同点，它们各自关注的评估维度是什么？</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -170,22 +142,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>SETR模型中的信息需求识别（IRI）模块是如何工作的？它如何帮助进行段落选择？</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>SETR模型结合了链式思维推理和显式信息需求识别（IRI）。IRI模块帮助模型识别不同的信息需求，然后相应地执行段落选择。完整的SETR-CoT &amp; IRI模型既包含CoT推理，又包含显式的信息需求识别，从而实现更有效的段落选择。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve"> "SETR-CoT &amp; IRI is the full model that incorporates both CoT reasoning and explicit information requirement identification, and performs passage selection accordingly"</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>论文 2025.acl-long.861.pdf（SETR），第4页</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t xml:space="preserve"> 什么是SYNQA方法？它的核心目标是什么？</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -202,38 +158,11 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>RHIO框架的三个主要组成部分是什么？请详细说明每个组件的功能。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>RHIO框架包含三个主要组件：
-1.不忠实数据增强（Unfaithful Data Augmentation）：通过选择性屏蔽检索头来生成不忠实的样本，模拟模型内在错误
-2.忠实度感知调优（Faithfulness-Aware Tuning）：利用不忠实响应和忠实响应进行联合训练，使模型能够区分不忠实输出
-3.自诱导解码（Self-Induced Decoding）：利用控制令牌进行对比解码，放大忠实与不忠实输出之间的差异</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>"RHIO consists of three main components: unfaithful data augmentation, faithfulness-aware tuning, and self-induced decoding."</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>在HALoGEN基准测试中，表现最好的LLM在响应式任务上的幻觉率是多少？</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve"> 在响应式任务上，表现最好的LLM（GPT-3.5和GPT-4）的幻觉率在3%-86%之间，具体取决于领域。即使是表现最好的模型也会产生相当数量的事实错误。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>"We find that all LLMs make a considerable number of factual errors, with even the best-performing LLMs hallucinating between 3%-86% of the facts generated, depending on the domain."</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>比较SYNQA和RHIO两种方法在提升模型性能方面的不同策略。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>SYNQA：专注于生成合成训练数据来训练上下文归因模型，通过实体中心和对话中心的样本生成，使小模型能够缩小与大模型的差距;RHIO：专注于提升上下文忠实度，通过检索头诱导优化，教模型明确区分忠实和不忠实的生成，甚至超越GPT-4o的表现</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -310,30 +239,14 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>什么是Agentic Reasoning框架？它的核心创新点是什么？</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>Agentic Reasoning是一个通过集成外部工具使用代理来增强大型语言模型推理的框架。</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t xml:space="preserve"> "We introduce Agentic Reasoning, a framework that enhances large language model (LLM) reasoning by integrating external tool-using agents</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>2025.acl-long.1383.pdf (第1页)</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t xml:space="preserve"> AR-MCTS算法中的"Knowledge Concept Filter"是如何工作的？</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve"> Knowledge Concept Filter通过使用InsTag（一个开放世界的标签器）对知识库进行离线概念标注，然后进行一致性筛选。对于文本数据直接使用InsTag标注，对于多模态数据先用MLLM生成图像描述，再用InsTag进行标注，最后进行一致性筛选。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>在Humanity's Last Exam数据集上，Agentic Reasoning与DeepSeek-R1结合的性能提升是多少？</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -354,10 +267,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>CypherBench基准测试是如何解决传统KBQA基准测试的局限性的？</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t xml:space="preserve"> REAL-MM-RAG基准测试的四个关键属性是什么？</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -402,10 +311,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>比较REAL-MM-RAG和LongDocURL两个基准测试在评估多模态检索能力时的侧重点差异。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>REAL-MM-RAG专注于真实世界的多模态文档检索，强调四个关键属性：多模态文档、增强难度、真实RAG查询和准确标注，并使用基于查询改写的多难度级别方案。LongDocURL则专注于长文档理解，将问题分为理解、推理和定位三类任务，并根据证据元素类型（文本、布局、图表、表格）和页面数量（单页、多页、跨元素）进行细分，共20个子任务。</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -426,10 +331,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>2025.acl-long.140_A Survey of Post-Training Scaling in Large Language Models, 第2页</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>在论文"A Survey of Post-Training Scaling in Large Language Models"中，作者将post-training scaling分为哪三个主要类型？</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -458,32 +359,15 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>"Post-training can be categorized into three main types: Supervised Fine-tuning: The LLM is trained to map input instructions to output labels. Reinforcement Learning: The LLM generates outputs based on input instructions, receives reward signals from the environment, and updates itself according to these rewards. Test-time Compute: The LLM utilizes computation and inference strategies to enhance performance across various scenarios."</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>2025.acl-long.1574_CiteEval , 第7页</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>论文 2025.acl-long.250.pdf（NoiserBench），第15页</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>2025.acl-long.1062_FaithfulRAG ,第7页</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>UniRAG提出统一的查询理解框架，集成查询增强和查询编码两个阶段；FaithfulRAG专注于知识冲突解决，通过动态协调参数化知识和上下文知识来提高语义一致性。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>《FaithfulRAG》与《Astute RAG》均旨在缓解检索增强生成中的知识冲突，二者在冲突调和范式上有何核心区别？</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>《FaithfulRAG》,第3页
-《Astute RAG》, 第3页</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -505,10 +389,6 @@
   </si>
   <si>
     <t xml:space="preserve"> 2025.acl-long.180.pdf (第22页)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve"> CypherBench通过将RDF图转换为多个领域特定的属性图并使用Cypher查询它们来解决传统KBQA基准测试的局限性</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -530,18 +410,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t xml:space="preserve"> "we propose Self-Guided Monte Carlo Tree Search (SG-MCTS), which capitalizes on the self-reflection capability of LLMs to reason about the intermediate states of MCTS for guiding the tree expansion process" </t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ASTUTE RAG的定义是什么？</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ASTUTE RAG是一种新型的检索增强生成方法，旨在使大语言模型对不完美的检索增强具有弹性。该方法通过三个核心步骤实现：首先自适应地从LLMs的内部知识中提取关键信息，然后以来源感知的方式迭代整合内部和外部知识，最后根据信息可靠性确定最终答案。它能够有效识别一致信息、检测冲突信息并过滤无关信息，从而解决知识冲突问题，提高RAG系统的可靠性和可信度。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>"To render LLMs resilient to imperfect retrieval, we propose ASTUTE RAG, a novel RAG approach that adaptively elicits essential information from LLMs' internal knowledge, iteratively consolidates internal and external knowledge with source-awareness, and finalizes the answer according to information reliability."</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -550,16 +418,7 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>根据实验结果，RankCoT 模型在性能提升和推理效率方面相较于原始 RAG 模型有哪些具体优势？</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>论文 2025.acl-long.629.pdf（RankCoT），第6页</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>根据实验结果，RankCoT 的优势主要体现在以下两个方面：
-性能提升： RankCoT 相较于原始 RAG 模型提升了 2.5%，证明其能通过更有意义的知识精炼帮助大语言模型更好地回答问题。</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -643,20 +502,7 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>在检索增强生成（RAG）系统中，SYNQA和QAEncoder各自解决的核心问题是什么？</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>SYNQA解决的是如何为大型语言模型（LLM）生成的答案提供支持证据的问题。具体来说，LLMs有时会产生错误或误导性的回答（即幻觉），因此将生成的答案与上下文提供的信息进行关联——即为生成的文本提供证据——对于LLMs的可信度至关重要。
-QAEncoder解决的是用户查询和相关文档之间固有的差距问题，这种差距阻碍了精确匹配。这个差距存在于词汇、句法、语义和内容等多个维度，严重影响了检索增强生成（RAG）系统的检索效果。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>2025.acl-long.828_On Synthesizing Data for Context Attribution in Question Answering, 第1页; 2025.acl-long.217_QAEncoder.pdf, 第1页</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>比较LongBench v2和AGENTGYM两个定义的主要区别和应用场景。</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -677,15 +523,7 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t xml:space="preserve">"We define and categorize seven types of RAG noise into beneficial and harmful groups" </t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>RAG噪声被分为有益噪声（beneficial noise）和有害噪声（harmful noise）。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve"> "LongRefiner"使用什么特殊标签来省略内容？</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -711,67 +549,11 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>"In this work, we propose UniRAG, a unified framework for query understanding in RAG. UniRAG employs a decoder only LLM to jointly perform query augmentation and encoding, eliminating task separation.";
- "This backbone-agnostic efficacy highlights its ability to harmonize parametric and contextual knowledge dynamically, regardless of model architecture and context complexity."</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve"> "Agentic Reasoning dynamically leverages web search, code execution, and structured memory to address complex problems requiring deep research. A key innovation in our framework is the Mind-Map agent, which constructs a structured knowledge graph to store reasoning context and track logical relationships.";
- "we propose AR-MCTS, a universal framework designed to progressively improve the reasoning capabilities of MLLMs through Active Retrieval (AR) and Monte Carlo Tree Search (MCTS)AR-MCTS follows the MCTS algorithm and heuristically integrates an active retrieval mechanism during the expansion stage to automatically acquire high-quality step-wise reasoning annotations."</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>"The adapter learns to dynamically reweight attention based on contextual relevance and consistency signals without explicit conflict extraction... Our method operates within a single generation pass."; 
-"Astute RAG explicitly models knowledge conflicts at the fact level via Self-Fact Mining... It then employs a Self-Think mechanism that forces the model to generate an interpretable reasoning trace before answering, justifying how each conflict is resolved."</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>We find that SFT with standard, short-context instruction datasets is sufficient for achieving good performance.Contrary to previous study, long synthetic instruction data does not further boost the performance.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>"Therefore, we introduce a &lt;skip&gt; to represent omitted content, retaining only the first and last k tokens of each paragraph while replacing the omitted content with &lt;skip&gt; . "</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>"To address the aforementioned challenges, we propose transforming the RDF graph into multiple domain-specific property graphs and using Cypher to query them (see Figure 2 for an illustration). We chose Cypher, the query language for Neo4j, because of its widespread adoption in open-source projects (including LLM frameworks and GraphRAG)."</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>"We introduce QAEncoder, a training-free approach to bridge this gap. Specifically, QAEncoder estimates the expectation of potential queries in the embedding space as a robust surrogate for the document embedding, and attaches document fingerprints to effectively distinguish these embeddings. ."</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>"This dataset encompasses a range of texts and RAG questions across three critical domains—finance, law, and medical—chosenfor their real-world importance. In addition, thedataset features both Chinese and English texts,serving as a comprehensive resource for multilingual, scenario-specific research. Overall, thedataset contains 6,711 questions, reflecting its extensive scale and diversity."</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>"Only GPT-4o meets the passing standard and scores highest at 64.5, indicating that our LongDocURL presents significant challenges for current models. (2) Comparison of Open-source and Closed-source models: Proprietary models demonstrate better overall performance compared to open source models. Among open-source models, only Qwen2-VL (score 30.6) and LLaVA-OneVision(scores 22.0 and 25.0) exceed a score of 20, while other models with fewer than 13B parameters fall below this threshold."</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve"> "MEMERAG: a Multilingual End-to-end Meta-Evaluation RAG benchmark(MEMERAG). Our benchmark builds on the popular MIRACL dataset, using native language questions and generating responses with diverse large language models (LLMs), which are then assessed by expert annotators for faithfulness and relevance. " ;
- "DragonBall dataset, which stands for Diverse RAG Omni-Benchmark for All scenarios"</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve"> "a novel generative strategy for synthesizing context attribution data";
-"RHIO first augments unfaithful samples that simulate realistic model-intrinsic errors by selectively masking retrieval heads."</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve"> "LongBench v2 consists of 503 challenging multiple-choice questions, with contexts ranging from 8k to 2M words, across six major task categories.";
- "However, the community lacks a unified interactive framework that covers diverse environments for comprehensive evaluation of agents, and enables exploration and learning for their self-improvement. To address this, we propose AGENTGYM, a framework featuring 7 real-world scenarios, 14 environments, and 89 tasks for unified, real-time, and concurrent agent interaction.."</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve"> "We introduce REAL-MM-RAG, an automatically generated benchmark designed to address four key properties essential for real-world retrieval: (i) multi-modal documents, (ii) enhanced difficulty, (iii) Realistic-RAG queries and (iv) accurate labeling.";
-"Firstly, each question-answering pair can be categorized by three primary tasks: Understanding, Reasoning, and Locating... Secondly, we define four types of answer evidences based on element type: (1) Text: pure texts, such as paragraph; (2) Layout: text elements with special layout meaning; (3) Figure: including charts and general images; (4) Table... Based on different primary tasks and answer evidences, we divide our dataset into 20 sub-tasks."</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>"LLMs sometimes produce false or misleading responses, also known as hallucinations. Therefore, grounding the generated answers in contextually provided information—i.e., providing evidence for the generated text—is paramount for LLMs' trustworthiness.";
-"However, the inherent gap between user queries and relevant documents hinders precise matching... termed the document-query gap. Three main approaches have emerged to address this challenge: training-based, document-centric and query-centric alignment."</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -790,18 +572,240 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>. Astute RAG：源感知的主动知识整合范式
-核心机制： 采用 “先整合，后生成” 的策略。它强调在生成答案之前，通过一个显式的“源感知知识整合”过程来预处理知识。
-冲突处理方式： 将冲突解决视为一个独立的知识清洗阶段。通过合并一致信息、识别冲突信息和过滤无关信息这三个步骤，主动对检索内容和模型内部知识进行比对与裁决，构建出一个无冲突的、一致的知识上下文供后续生成使用。
-侧重点： 侧重于输入端的质量控制，试图在生成前消除知识源之间的不一致性。
-2. FaithfulRAG：基于忠实度约束的生成对齐范式
-核心机制： 采用 “生成时约束” 或 “后验证” 的策略。其核心在于确保生成的答案严格忠实于给定的检索证据，而非在生成前强行统一所有知识源。
-冲突处理方式： 将冲突处理内化为生成过程中的忠实度保障机制。当检索文档与模型参数知识冲突时，它倾向于通过训练目标或解码约束，强制模型优先遵循检索到的外部证据，抑制模型内部可能过时或错误的记忆，而不是试图去“调和”两者以达成一致。
-侧重点： 侧重于输出端的可靠性与可溯源性，承认冲突的存在，但通过约束生成行为来保证答案对特定来源（通常是检索文档）的忠实度。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>无法回答。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>"Through empirical evaluation of eight representative LLMs with diverse architectures and scales, we reveal that these noises can be further categorized into two practical groups: noise that is beneficial to LLMs
+(aka beneficial noise) and noise that is harmful to LLMs (aka harmful noise)."</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>论文 2025.acl-long.250.pdf（NoiserBench），第1页</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve"> "We introduce Agentic Reasoning, a framework that enhances large language model (LLM) reasoning by integrating external tool-using agents."</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>什么是Agentic Reasoning框架?</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>为了使大语言模型对不完美的检索结果更具鲁棒性，我们提出了 ASTUTE RAG，这是一种新颖的检索增强生成方法。该方法能够自适应地从大语言模型的内部知识中提取关键信息，在感知信息来源的基础上迭代整合内外部知识，并根据信息的可靠性最终生成答案。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ASTUTE RAG的定义是什么？有什么用?</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>"We find that SFT with standard, short-context instruction datasets is sufficient for achieving good performance.Contrary to previous study, long synthetic instruction data does not further boost the performance."</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SG-MCTS利用LLMs的自反思能力来推理MCTS的中间状态，以指导树扩展过程。在每次迭代中，SG-MCTS 遵循四个步骤，即选择、反思引导的扩展、评估和反向传播。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve"> Think&amp; Cite框架中的Self-Guided Monte Carlo Tree Search (SG-MCTS)如何工作？有几个步骤?</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>论文 2025.acl-long.490.pdf（Think&amp; Cite），第1页, 第4页</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SETR 的段落选择提示（Passage Selection Prompt）所引导的关键过程包含哪三个具体步骤？每个步骤的核心任务是什么？</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>该关键过程包含以下三个步骤及其核心任务：
+枚举关键信息需求： 核心任务是列出回答当前问题所必需的关键信息点；
+识别相关段落： 核心任务是针对每一个已枚举的信息需求，找出包含相关信息的段落；
+选择最优段落子集： 核心任务是从候选段落中挑选出一个子集，使其在整体上能提供最全面且多样化的信息覆盖，从而有效回答查询。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>"The key process consists of three key steps: (1) enumerating the Passage Selection Prompt of SETR key information requirements necessary to answer the question; (2) identifying passages that contain relevant information for each requirement; and (3) selecting a subset of passages that collectively provide the most comprehensive and diverse coverage to effectively answer the query.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>论文 2025.acl-long.861.pdf（SETR），第3页</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>CypherBench 是如何从 RDF 图生成领域特定属性图的？</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>CypherBench 通过将 RDF 图转换为多个领域特定的属性图（domain-specific property graphs）来实现这一过程，并使用 Cypher 语言对其进行查询。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>"To address the aforementioned challenges, we propose transforming the RDF graph into multiple domain-specific property graphs and using Cypher to query them."</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>根据实验结果，RankCoT 模型相较于原始 RAG 模型有哪些具体优势？</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>RankCoT 模型相较于原始 RAG 模型的具体优势体现在以下两方面：
+量化性能提升：实验结果显示，RankCoT 的性能比原始 RAG 模型提高了 2.5%。
+优化机制优势：该模型能够提供更有效的精炼信息（more meaningful refinements），从而帮助大语言模型更好地回答问题。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>实验结果表明，RAGEval 的机器自动评估与人工评估在所有指标上均表现出高度一致性。两者之间的最终绝对差异仅为 1.67%，且三位标注者之间的 Fleiss’ Kappa 值达到了 0.7686，验证了该自动评估指标的可靠性及其与人类判断的一致性。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>RAGEval 提出的自动评估指标与人工评估的一致性如何？</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>"Results in Figure 7 show that the machine and human evaluations show a high degree of alignment in all metrics. The final absolute difference between the human evaluation and the machine evaluation is 1.67%. The Fleiss’ Kappa value between the three annotators is 0.7686."</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2025.acl-long.418_RAGEval.pdf, 第11页</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>在 HALoGEN 基准测试中，表现最好的 LLM 生成事实的幻觉率范围是多少？</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>实验发现，即使是表现最好的 LLM，其生成事实的幻觉率也在 3% 到 86% 之间，具体数值取决于所属领域。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>在利用大模型内部知识应对知识冲突时，《Astute RAG》与《FaithfulRAG》各自采用了什么核心机制/模块来提取或生成内部知识？</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>《Astute RAG》：采用自适应段落生成（Adaptive Generation of Internal Knowledge / Adaptive Passage Generation） 机制，通过提示大模型直接生成包含内部知识的段落（passages），并允许模型自适应决定生成的段落数量。
+《FaithfulRAG》：采用自我事实挖掘 模块，通过外部化大模型对问题的理解，提取出细粒度的、事实级别的内部知识。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>"FaithfulRAG adopts a novel self-fact mining module to externalize the LLM’s understanding of the question, obtaining fine-grained knowledge at the fact level."
+"ASTUTE RAG starts from acquiring the most accurate, relevant, and thorough passage set from the LLMs’ internal knowledge."</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>《FaithfulRAG》,第2页
+《Astute RAG》, 第5页</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>"We show that the attribution data synthesized via SYNQA is highly effective for fine-tuning small LMs for context attribution in different QA tasks and domains"
+"RHIO first augments unfaithful samples that simulate realistic model-intrinsic errors by selectively masking retrieval heads. Then, these samples are incorporated into joint training, enabling the model to distinguish unfaithful outputs from faithful ones conditioned on control tokens."</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SYNQA：通过 SYNQA 合成的训练数据在对小型语言模型进行微调以实现不同问答任务和领域的上下文归因时非常有效;
+RHIO：负向数据增强与错误模拟。通过选择性地掩码检索头，故意制造出“不忠实”的样本，以模拟模型在真实情况下的内在错误, 然后将正常样本与这些构造出的错误样本放在一起进行联合训练，并引入“控制标记”。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>比较LongBench v2和AGENTGYM应用场景区别。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>比较LongDocURL与REAL-MM-RAG这两个基准测试在构建评估体系（或任务设计）时的侧重点差异</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>《QAEncoder》侧重于“检索阶段”
+核心痛点：用户的自然语言查询与知识库中的文档之间存在语义和词汇上的鸿沟，导致检索模块无法精准召回相关文档。
+《On Synthesizing Data for Context Attribution... (SYNQA)》侧重于“生成后阶段”
+核心痛点：大语言模型在生成答案时容易产生幻觉，用户很难验证生成的答案是否真的基于提供的上下文，缺乏可解释性和事实依据。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>"Despite advancements, a significant challenge that persists is bridging the gap between user queries and documents across lexical, syntactic, semantic, and content dimensions(Zheng et al., 2020;Nogueira et al., 2019; Cheriton, 2019),termed the document-query gap."
+"However, LLMs sometimes produce false or misleading responses, also known as hallucinations."</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve"> "MEMERAG: a Multilingual End-to-end Meta-Evaluation RAG benchmark(MEMERAG). Our benchmark builds on the popular MIRACL dataset, using native language questions and generating responses with diverse large language models (LLMs), which are then assessed by expert annotators for faithfulness and relevance. " 
+ "DragonBall dataset, which stands for Diverse RAG Omni-Benchmark for All scenarios"</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>"In this work, we propose UniRAG, a unified framework for query understanding in RAG. UniRAG employs a decoder only LLM to jointly perform query augmentation and encoding, eliminating task separation."
+ "This backbone-agnostic efficacy highlights its ability to harmonize parametric and contextual knowledge dynamically, regardless of model architecture and context complexity."</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve"> "LongBench v2 consists of 503 challenging multiple-choice questions, with contexts ranging from 8k to 2M words, across six major task categories."
+ "However, the community lacks a unified interactive framework that covers diverse environments for comprehensive evaluation of agents, and enables exploration and learning for their self-improvement. To address this, we propose AGENTGYM, a framework featuring 7 real-world scenarios, 14 environments, and 89 tasks for unified, real-time, and concurrent agent interaction."</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve"> "Agentic Reasoning dynamically leverages web search, code execution, and structured memory to address complex problems requiring deep research. A key innovation in our framework is the Mind-Map agent, which constructs a structured knowledge graph to store reasoning context and track logical relationships."
+ "we propose AR-MCTS, a universal framework designed to progressively improve the reasoning capabilities of MLLMs through Active Retrieval (AR) and Monte Carlo Tree Search (MCTS)AR-MCTS follows the MCTS algorithm and heuristically integrates an active retrieval mechanism during the expansion stage to automatically acquire high-quality step-wise reasoning annotations."</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve"> "We introduce REAL-MM-RAG, an automatically generated benchmark designed to address four key properties essential for real-world retrieval: (i) multi-modal documents, (ii) enhanced difficulty, (iii) Realistic-RAG queries and (iv) accurate labeling."
+"Firstly, each question-answering pair can be categorized by three primary tasks: Understanding, Reasoning, and Locating, as discussed in Section 1. Secondly, we define four types of answer evidences based on element type: (1) Text: pure texts, such as paragraph; (2) Layout: text elements with special layout meaning (generalized text), such as title, header, footer, table name and figure name; (3) Figure: including charts and general images. (4) Table. In addition, each question-answering pair can be classified into single-page or multi-page based on the number of answer evidence pages and single element or cross-element based on the number of types of evidence elements. Based on different primary tasks and answer evidences, we divide our dataset into 20 sub-tasks."</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>"The teacher LLM is usually heavy in size and deployed on the cloud, and the student is on local devices. It is simple to develop methods for preserving privacy using our proposed framework by transmitting only de-identified queries and structured knowledge instead of full responses, as we have introduced in Section 3.3."</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>"we propose Self-Guided Monte Carlo Tree Search (SG-MCTS), which capitalizes on the self-reflection capability of LLMs to reason about the intermediate states of MCTS for guiding the tree expansion process." 
+"In each iteration, SG-MCTS follows four steps, i.e., selection, reflection-guided expansion, evaluation, and backpropagation."</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>RHIO框架的三个主要组成部分是什么？</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>RHIO框架包含三个主要组件：
+1.不忠实数据增强（Unfaithful Data Augmentation）
+2.忠实度感知调优（Faithfulness-Aware Tuning）
+3.自诱导解码（Self-Induced Decoding）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">"RHIO consists of three main components: unfaithful data augmentation, faithfulness-aware tuning, and self-induced decoding."
+</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve"> "LongRefiner"使用什么特殊标签来省略冗余内容？</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>"Since most tokens in the flat representation are derived from the original document, we can omit redundant content and restore it during structure recovery. Therefore, we introduce a &lt;skip&gt; tag to represent omitted content, retaining only the first and last k tokens of each paragraph while replacing the omitted content with &lt;skip&gt;."</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>AR-MCTS算法中，为确保概念过滤的可扩展性，作者采用了什么具体策略来实现离线知识概念标注与一致性过滤？</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>作者采用开放世界标注工具 TaggerInsTag 进行离线知识概念标注，并复用前述流程执行一致性过滤，以此确保概念过滤的可扩展性。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>在构建可靠的问答（QA）系统时，这QAEncoder与On Synthesizing Data for Context Attribution in Question Answering两篇论文分别侧重于优化系统工作流的哪个阶段？它们各自试图解决的核心痛点是什么？</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>" Our survey categorizes post-training scaling into three key methodologies:Supervised Fine-tuning (SFT), Reinforcement Learning from Feedback (RLxF), and Test-time Compute (TTC)."</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2025.acl-long.140_A Survey of Post-Training Scaling in Large Language Models, 第1页</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1155,7 +1159,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D11"/>
+  <dimension ref="A1:D13"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="49.83203125" style="1" customWidth="1"/>
@@ -1179,144 +1183,172 @@
         <v>14</v>
       </c>
     </row>
-    <row r="2" spans="1:4" ht="126" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:4" ht="56" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
-        <v>96</v>
+        <v>72</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>159</v>
+        <v>120</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>103</v>
+        <v>180</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>95</v>
+        <v>181</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="84" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
-        <v>160</v>
+        <v>121</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>161</v>
+        <v>122</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>162</v>
+        <v>123</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" ht="42" x14ac:dyDescent="0.3">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" ht="84" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
-        <v>158</v>
+        <v>119</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>156</v>
+        <v>118</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>155</v>
+        <v>130</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>105</v>
+        <v>131</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="112" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B5" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="B5" s="1" t="s">
+      <c r="C5" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="C5" s="1" t="s">
+      <c r="D5" s="1" t="s">
         <v>21</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>22</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="84" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
-        <v>36</v>
+        <v>25</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>37</v>
+        <v>26</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>38</v>
+        <v>27</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>39</v>
+        <v>28</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="126" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
-        <v>49</v>
+        <v>32</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>50</v>
+        <v>33</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>51</v>
+        <v>34</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>52</v>
+        <v>35</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="42" x14ac:dyDescent="0.3">
       <c r="A8" s="3" t="s">
-        <v>66</v>
+        <v>133</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>67</v>
+        <v>49</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>68</v>
+        <v>132</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>69</v>
+        <v>50</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="126" x14ac:dyDescent="0.3">
       <c r="A9" s="3" t="s">
-        <v>78</v>
+        <v>56</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>79</v>
+        <v>57</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>80</v>
+        <v>58</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>81</v>
+        <v>59</v>
       </c>
     </row>
     <row r="10" spans="1:4" ht="98" x14ac:dyDescent="0.3">
       <c r="A10" s="3" t="s">
-        <v>121</v>
+        <v>135</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>122</v>
+        <v>134</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>123</v>
+        <v>91</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>124</v>
+        <v>92</v>
       </c>
     </row>
     <row r="11" spans="1:4" ht="154" x14ac:dyDescent="0.3">
       <c r="A11" s="3" t="s">
-        <v>129</v>
+        <v>95</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>130</v>
+        <v>96</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>131</v>
+        <v>97</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>132</v>
+        <v>98</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" ht="42" x14ac:dyDescent="0.3">
+      <c r="A12" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" ht="56" x14ac:dyDescent="0.3">
+      <c r="A13" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>84</v>
       </c>
     </row>
   </sheetData>
@@ -1327,7 +1359,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{466533FD-94F5-4649-A3FC-D49F5C1CDCDD}">
-  <dimension ref="A1:D14"/>
+  <dimension ref="A1:D12"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="50.83203125" style="1" customWidth="1"/>
@@ -1353,16 +1385,16 @@
     </row>
     <row r="2" spans="1:4" ht="98" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
-        <v>100</v>
+        <v>76</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>101</v>
+        <v>77</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>166</v>
+        <v>136</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>102</v>
+        <v>78</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="112" x14ac:dyDescent="0.3">
@@ -1370,167 +1402,139 @@
         <v>3</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>177</v>
+        <v>126</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>178</v>
+        <v>127</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" ht="84" x14ac:dyDescent="0.3">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" ht="112" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
-        <v>157</v>
+        <v>175</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>167</v>
+        <v>176</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" ht="70" x14ac:dyDescent="0.3">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" ht="112" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
         <v>15</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>110</v>
+        <v>82</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>16</v>
+        <v>170</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" ht="84" x14ac:dyDescent="0.3">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" ht="112" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
-        <v>23</v>
+        <v>138</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>24</v>
+        <v>137</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>120</v>
+        <v>171</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" ht="84" x14ac:dyDescent="0.3">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" ht="154" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
-        <v>32</v>
+        <v>140</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>33</v>
+        <v>141</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>34</v>
+        <v>142</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" ht="154" x14ac:dyDescent="0.3">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" ht="126" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" ht="56" x14ac:dyDescent="0.3">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" ht="70" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
-        <v>53</v>
+        <v>177</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>54</v>
+        <v>178</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>55</v>
+        <v>85</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" ht="126" x14ac:dyDescent="0.3">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" ht="56" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" ht="210" x14ac:dyDescent="0.3">
+      <c r="A11" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="B10" s="1" t="s">
+      <c r="B11" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="C10" s="1" t="s">
+      <c r="C11" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="D10" s="1" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" ht="84" x14ac:dyDescent="0.3">
-      <c r="A11" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="C11" s="1" t="s">
-        <v>113</v>
-      </c>
       <c r="D11" s="1" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" ht="126" x14ac:dyDescent="0.3">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" ht="154" x14ac:dyDescent="0.3">
       <c r="A12" s="1" t="s">
-        <v>77</v>
+        <v>69</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>115</v>
+        <v>90</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>168</v>
+        <v>124</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" ht="210" x14ac:dyDescent="0.3">
-      <c r="A13" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="B13" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="C13" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="D13" s="1" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" ht="154" x14ac:dyDescent="0.3">
-      <c r="A14" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="B14" s="1" t="s">
-        <v>119</v>
-      </c>
-      <c r="C14" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="D14" s="1" t="s">
-        <v>118</v>
+        <v>89</v>
       </c>
     </row>
   </sheetData>
@@ -1574,7 +1578,7 @@
         <v>6</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>104</v>
+        <v>79</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="56" x14ac:dyDescent="0.3">
@@ -1588,133 +1592,133 @@
         <v>11</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" ht="70" x14ac:dyDescent="0.3">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" ht="98" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
-        <v>125</v>
+        <v>147</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>127</v>
+        <v>148</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>128</v>
+        <v>94</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" ht="126" x14ac:dyDescent="0.3">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" ht="70" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
-        <v>26</v>
+        <v>153</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>27</v>
+        <v>154</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>170</v>
+        <v>29</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>28</v>
+        <v>99</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="70" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="D6" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="B6" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" ht="70" x14ac:dyDescent="0.3">
+    </row>
+    <row r="7" spans="1:4" ht="266" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
-        <v>57</v>
+        <v>100</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>58</v>
+        <v>101</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>59</v>
+        <v>102</v>
       </c>
       <c r="D7" s="1" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" ht="70" x14ac:dyDescent="0.3">
+      <c r="A8" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" ht="98" x14ac:dyDescent="0.3">
+      <c r="A9" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" ht="140" x14ac:dyDescent="0.3">
+      <c r="A10" s="1" t="s">
         <v>60</v>
       </c>
-    </row>
-    <row r="8" spans="1:4" ht="266" x14ac:dyDescent="0.3">
-      <c r="A8" s="1" t="s">
-        <v>134</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>135</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>136</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" ht="70" x14ac:dyDescent="0.3">
-      <c r="A9" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="D9" s="1" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" ht="98" x14ac:dyDescent="0.3">
-      <c r="A10" s="1" t="s">
-        <v>75</v>
-      </c>
       <c r="B10" s="1" t="s">
-        <v>139</v>
+        <v>61</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>76</v>
+        <v>62</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" ht="140" x14ac:dyDescent="0.3">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" ht="168" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="s">
-        <v>82</v>
+        <v>107</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>83</v>
+        <v>68</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>84</v>
+        <v>125</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" ht="168" x14ac:dyDescent="0.3">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" ht="98" x14ac:dyDescent="0.3">
       <c r="A12" s="1" t="s">
-        <v>141</v>
+        <v>150</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>91</v>
+        <v>149</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>171</v>
+        <v>151</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>142</v>
+        <v>152</v>
       </c>
     </row>
   </sheetData>
@@ -1747,18 +1751,18 @@
         <v>14</v>
       </c>
     </row>
-    <row r="2" spans="1:4" ht="322" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:4" ht="112" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
-        <v>108</v>
+        <v>155</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>180</v>
+        <v>156</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>165</v>
+        <v>157</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>109</v>
+        <v>158</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="126" x14ac:dyDescent="0.3">
@@ -1766,97 +1770,97 @@
         <v>8</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>107</v>
+        <v>81</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>154</v>
+        <v>117</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="126" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>143</v>
+        <v>109</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>172</v>
+        <v>165</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" ht="70" x14ac:dyDescent="0.3">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" ht="126" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>47</v>
+        <v>160</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>173</v>
+        <v>159</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>145</v>
+        <v>111</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="154" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
-        <v>150</v>
+        <v>161</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>61</v>
+        <v>44</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>174</v>
+        <v>167</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>151</v>
+        <v>114</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="182" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
-        <v>88</v>
+        <v>66</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>153</v>
+        <v>116</v>
       </c>
       <c r="C7" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" ht="280" x14ac:dyDescent="0.3">
+      <c r="A8" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" ht="126" x14ac:dyDescent="0.3">
+      <c r="A9" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="C9" s="1" t="s">
         <v>164</v>
       </c>
-      <c r="D7" s="1" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" ht="196" x14ac:dyDescent="0.3">
-      <c r="A8" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>175</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" ht="154" x14ac:dyDescent="0.3">
-      <c r="A9" s="1" t="s">
-        <v>147</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>148</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>176</v>
-      </c>
       <c r="D9" s="1" t="s">
-        <v>149</v>
+        <v>113</v>
       </c>
     </row>
   </sheetData>
@@ -1893,13 +1897,13 @@
         <v>12</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>181</v>
+        <v>129</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="28" x14ac:dyDescent="0.3">
@@ -1907,97 +1911,97 @@
         <v>13</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>181</v>
+        <v>129</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="28" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="D4" s="2" t="s">
         <v>17</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>181</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>18</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="42" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>181</v>
+        <v>129</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="28" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
-        <v>48</v>
+        <v>31</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>181</v>
+        <v>129</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="28" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
-        <v>62</v>
+        <v>45</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>181</v>
+        <v>129</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="28" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
-        <v>93</v>
+        <v>70</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>181</v>
+        <v>129</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="28" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
-        <v>94</v>
+        <v>71</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>181</v>
+        <v>129</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
     </row>
   </sheetData>

--- a/code/测试集.xlsx
+++ b/code/测试集.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\rag_project\code\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9EBCE832-4838-4DCB-B419-5035A57A649E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{15C65696-AF9F-46D4-99FB-E135E66EF3B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="220" uniqueCount="182">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="220" uniqueCount="183">
   <si>
     <t>问题</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -118,18 +118,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>Ref-Long（Referencing Evaluation for Long-context Language Models）是一个专门设计用于评估长上下文语言模型（LCLMs）长上下文引用能力的基准。它要求LCLMs不仅要在给定文档中识别特定关键词，还要找出引用该关键词的文档索引，而不是其他相关但不匹配的文档。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>"this work proposes a novel benchmark called Referencing Evaluation for Long-context Language Models (Ref-Long), which is specifically designed to assess the long-context referencing capability of LCLMs. LCLMs are required to not only identify the specific key in the given documents, but also need to figure out the indexes of documents that reference the specific key"</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>论文 2025.acl-long.1162.pdf（Ref-Long），第2页</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>比较MEMERAG和DragonBall两个基准的异同点，它们各自关注的评估维度是什么？</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -142,22 +130,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t xml:space="preserve"> 什么是SYNQA方法？它的核心目标是什么？</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve"> SYNQA是一种生成合成训练数据的方法，用于训练上下文归因模型。它的核心目标是通过生成多样化的训练样本（包括实体中心和对话中心的样本），帮助模型发展强大的归因能力，使其能够跨不同上下文和领域进行泛化。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve"> "By generating both entity-centric and dialogue-centric samples, SYNQA produces training data that reflects the variety of real-world QA scenarios, helping models develop robust attribution capabilities, which our experiments demonstrate to generalize across different contexts and domains."</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>论文 2025.acl-long.828.pdf，第3页</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>"We find that all LLMs make a considerable number of factual errors, with even the best-performing LLMs hallucinating between 3%-86% of the facts generated, depending on the domain."</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -178,14 +150,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>"In this work, we introduce Agentic Long-Context Understanding (AgenticLU), a framework designed to enhance large language models' ability to process and reason over long-context inputs with self-generated data. By incorporating an agentic workflow (CoC) that dynamically refines model reasoning through self-clarifications and contextual grounding, AgenticLU significantly improves LLM's long context understanding capabilities."</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>论文 2025.acl-long.275.pdf，第8页</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t xml:space="preserve"> LongBench v2基准测试包含多少个问题？上下文长度范围是多少？</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -194,27 +158,11 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>"LongBench v2 consists of 503 challenging multiple-choice questions, with contexts ranging from 8k to 2M words, across six major task categories."</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>论文 2025.acl-long.183.pdf，第1页</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t xml:space="preserve"> 在LongBench v2基准测试中，人类专家在15分钟时间限制下的准确率是多少？</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>人类专家在15分钟时间限制下的准确率为53.7%。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>"We employ both automated and manual review processes to maintain high quality and difficulty, resulting in human experts achieving only 53.7% accuracy under a 15-minute time constraint."</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve"> 论文 2025.acl-long.183.pdf，第1页</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -263,10 +211,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>"On GAIA, Agentic Reasoning establishes a new SOTA among all publicly available methods. Compared to OpenAI's Deep Research, which leverages its proprietary high-performance reasoning models, our approach surpasses it on Level 1 and Level 2 tasks while narrowing the gap to 2.26% on Level 3."</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t xml:space="preserve"> REAL-MM-RAG基准测试的四个关键属性是什么？</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -275,14 +219,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t xml:space="preserve"> "We introduce REAL-MM-RAG, an automatically generated benchmark designed to address four key properties essential for real-world retrieval: (i) multi-modal documents, (ii) enhanced difficulty, (iii) Realistic-RAG queries and (iv) accurate labeling. Additionally, we propose a multi-difficulty-level scheme based on query rephrasing to evaluate models' semantic understanding beyond keyword matching."</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>2025.acl-long.1528.pdf (第1页)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t xml:space="preserve"> 在Asclepius医学基准测试中，人类医生与Med-MLLMs的表现对比如何？</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -319,10 +255,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t xml:space="preserve"> DocQuery方法如何解决文档-查询差距问题？</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>Agentic Reasoning框架中使用的Mind-Map agent的具体神经网络架构是什么？</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -331,18 +263,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>在论文"A Survey of Post-Training Scaling in Large Language Models"中，作者将post-training scaling分为哪三个主要类型？</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>safeRAG论文, 第二页</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>2025.acl-long.1476_Astute RAG, 第5页</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>2025.acl-long.176_Hierarchical Document Refinement for Long-context Retrieval-augmented Generation ,第四页</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -355,31 +275,11 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>论文How to Train Long-Context Language Models (Effectively),第2页</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>2025.acl-long.1574_CiteEval , 第7页</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>2025.acl-long.1062_FaithfulRAG ,第7页</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>UniRAG提出统一的查询理解框架，集成查询增强和查询编码两个阶段；FaithfulRAG专注于知识冲突解决，通过动态协调参数化知识和上下文知识来提高语义一致性。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>DRAG通过传输去标识化的查询和结构化知识而不是完整响应来保护用户隐私。这样可以避免传输完整的用户查询和敏感信息。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve"> 论文 2025.acl-long.358.pdf（DRAG），第5页</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>论文 2025.acl-long.826.pdf, 第15页</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -392,10 +292,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>2025.acl-long.438.pdf (第4页)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>2025.acl-long.540.pdf (第4页)</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -404,20 +300,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>QAEncoder采用了一种无需训练（training-free） 的方法来弥合文档与查询之间的差距。其核心机制包含两点：
-潜在查询期望估计： 在嵌入空间中估计潜在查询的期望值，将其作为文档嵌入的鲁棒替代表示（surrogate），从而使文档表示在语义上更贴近查询空间。
-文档指纹附加： 为这些嵌入表示附加文档指纹（document fingerprints），以有效区分不同文档的嵌入，避免仅依赖查询期望导致的文档辨识度丢失问题。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>"To render LLMs resilient to imperfect retrieval, we propose ASTUTE RAG, a novel RAG approach that adaptively elicits essential information from LLMs' internal knowledge, iteratively consolidates internal and external knowledge with source-awareness, and finalizes the answer according to information reliability."</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>2025.acl-long.1476_Astute RAG.pdf, 第1页</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>论文 2025.acl-long.629.pdf（RankCoT），第6页</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -434,10 +316,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>"To mitigate the above issues in long-context evaluation field, we propose an out-of-the-box evaluation suite, L-CiteEval, which requires LCMs to generate both the statements and their supporting evidence (citations). This suite comprises two key components: (1) a comprehensive benchmark encompassing 5 major task categories and 11 diverse long-context tasks, with context lengths ranging from 8K to 48K; and (2) corresponding automatic evaluation metrics and verification pipelines to ensure robust and reliable assessment."</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>2025.acl-long.263_L-CiteEval.pdf, 第一页</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -446,21 +324,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>AGENTSTAR方法在WebShop、ALFWorld和BabyAI任务上的性能如何？与GPT-4-Turbo相比有何优势？</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>AGENTSTAR方法在三个关键任务上表现出色：
-WebShop: 76.50%（比GPT-4-Turbo高61.00个百分点）
-ALFWorld: 88.00%（比GPT-4-Turbo高20.50个百分点）
-BabyAI: 82.70%（比GPT-4-Turbo高9.87个百分点）</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>"Through exploration and learning with AGENTSTAR, open-source models can handle diverse tasks and surpass SFT on most tasks. Although AGENTSTAR is initialized with limited trajectories, i.e., AGENTTRAJ, it is able to handle diverse tasks and achieve better performance than AGENTTRAJ-L-SFT by continuously exploring, receiving feedback, and learning in the environment. Moreover, it also performs on par with commercial models. For instance, agents with AGENTSTAR outperform GPT-4-Turbo and AGENTTRAJ-L-SFT by 61.00 and 3.00 points on WebShop (Yao et al., 2022), 20.50 and 5.00 points on ALFWorld (Shridhar et al., 2021), and 9.87 and 8.51 points on BabyAI (Chevalier-Boisvert et al., 2019). This validates the superiority and promise of the exploration and learning paradigm in developing agents (Zelikman et al., 2022)."</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>论文 2025.acl-long.1355.pdf，第7页</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -486,23 +349,6 @@
   </si>
   <si>
     <t>相同点：两者都是多语言RAG评估基准。不同点：MEMERAG专注于多语言端到端元评估，使用母语问题并由专家评估忠实度和相关性；DragonBall是一个多场景多语言RAG全能基准，涵盖金融、法律、医疗领域，包含6,711个问题，用于评估RAG系统在不同场景下的性能。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve"> 论文 2025.acl-long.1101.pdf(MEMERAG), 第1页; 2025.acl-long.418.pdf(DragonBall), 第4页</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>SYNQA: 2025.acl-long.828.pdf，第1页
-RHIO: 2025.acl-long.826.pdf，第1页</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Agentic Reasoning - 2025.acl-long.1383.pdf (第1页)；AR-MCTS - 2025.acl-long.180.pdf (第1页)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>2025.acl-long.828_On Synthesizing Data for Context Attribution in Question Answering, 第1页; 2025.acl-long.217_QAEncoder.pdf, 第1页</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -511,18 +357,10 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>REAL-MM-RAG - 2025.acl-long.1528.pdf (第1页)；LongDocURL - 2025.acl-long.57.pdf (第4页)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>Agentic Reasoning通过动态利用网络搜索、代码执行和结构化记忆来解决复杂问题，核心创新是Mind-Map agent构建知识图存储推理上下文。而AR-MCTS通过主动检索（AR）和蒙特卡洛树搜索（MCTS）逐步提升多模态大语言模型（MLLM）的推理能力，该框架遵循MCTS算法并在扩展阶段启发式地集成主动检索机制，以自动获取高质量的逐步推理注释。两者都使用外部工具增强推理，但Agentic Reasoning更注重工具集成和记忆管理，AR-MCTS更注重搜索策略和状态评估。</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t xml:space="preserve">2025.acl-long.693_UniRAG , 第1页 ;  2025.acl-long.1062_FaithfulRAG , 第7页 </t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>RAG噪声被分为有益噪声（beneficial noise）和有害噪声（harmful noise）。</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -531,21 +369,7 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>Supervised Fine-tuning (SFT), Reinforcement Learning (RLxF), and Test-time Compute (TTC).</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>在"safeRAG"论文中，作者定义的"silver noise"指什么？</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">Silver Noise（银色噪声 / 部分答案噪声）：
-指部分包含答案但不完整的上下文证据。与完全无关的噪声不同，这种噪声因为包含了部分正确答案，能够成功绕过大多数安全过滤器（Safety filters），进而稀释有用知识，破坏 RAG 系统生成回答的全面性和多样性。
-</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>"Firstly, we define silver noise (Fig. 1-②), which refers to evidence that partially contains the answer. Such noise can circumvent most safety filters, thereby undermining the RAG diversity(R-1)."</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -564,10 +388,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>"ASTUTE RAG first adaptively elicits LLMs' knowledge and then conducts source-aware knowledge consolidation. The desiderata is combining consistent information, identifying conflicting information, and filtering out irrelevant information."</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>论文 2025.acl-long.1481.pdf，第20页</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -576,19 +396,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>"Through empirical evaluation of eight representative LLMs with diverse architectures and scales, we reveal that these noises can be further categorized into two practical groups: noise that is beneficial to LLMs
-(aka beneficial noise) and noise that is harmful to LLMs (aka harmful noise)."</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>论文 2025.acl-long.250.pdf（NoiserBench），第1页</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve"> "We introduce Agentic Reasoning, a framework that enhances large language model (LLM) reasoning by integrating external tool-using agents."</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>什么是Agentic Reasoning框架?</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -601,19 +408,11 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>"We find that SFT with standard, short-context instruction datasets is sufficient for achieving good performance.Contrary to previous study, long synthetic instruction data does not further boost the performance."</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>SG-MCTS利用LLMs的自反思能力来推理MCTS的中间状态，以指导树扩展过程。在每次迭代中，SG-MCTS 遵循四个步骤，即选择、反思引导的扩展、评估和反向传播。</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t xml:space="preserve"> Think&amp; Cite框架中的Self-Guided Monte Carlo Tree Search (SG-MCTS)如何工作？有几个步骤?</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>论文 2025.acl-long.490.pdf（Think&amp; Cite），第1页, 第4页</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -644,20 +443,10 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>"To address the aforementioned challenges, we propose transforming the RDF graph into multiple domain-specific property graphs and using Cypher to query them."</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>根据实验结果，RankCoT 模型相较于原始 RAG 模型有哪些具体优势？</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>RankCoT 模型相较于原始 RAG 模型的具体优势体现在以下两方面：
-量化性能提升：实验结果显示，RankCoT 的性能比原始 RAG 模型提高了 2.5%。
-优化机制优势：该模型能够提供更有效的精炼信息（more meaningful refinements），从而帮助大语言模型更好地回答问题。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>实验结果表明，RAGEval 的机器自动评估与人工评估在所有指标上均表现出高度一致性。两者之间的最终绝对差异仅为 1.67%，且三位标注者之间的 Fleiss’ Kappa 值达到了 0.7686，验证了该自动评估指标的可靠性及其与人类判断的一致性。</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -683,26 +472,6 @@
   </si>
   <si>
     <t>在利用大模型内部知识应对知识冲突时，《Astute RAG》与《FaithfulRAG》各自采用了什么核心机制/模块来提取或生成内部知识？</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>《Astute RAG》：采用自适应段落生成（Adaptive Generation of Internal Knowledge / Adaptive Passage Generation） 机制，通过提示大模型直接生成包含内部知识的段落（passages），并允许模型自适应决定生成的段落数量。
-《FaithfulRAG》：采用自我事实挖掘 模块，通过外部化大模型对问题的理解，提取出细粒度的、事实级别的内部知识。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>"FaithfulRAG adopts a novel self-fact mining module to externalize the LLM’s understanding of the question, obtaining fine-grained knowledge at the fact level."
-"ASTUTE RAG starts from acquiring the most accurate, relevant, and thorough passage set from the LLMs’ internal knowledge."</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>《FaithfulRAG》,第2页
-《Astute RAG》, 第5页</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>"We show that the attribution data synthesized via SYNQA is highly effective for fine-tuning small LMs for context attribution in different QA tasks and domains"
-"RHIO first augments unfaithful samples that simulate realistic model-intrinsic errors by selectively masking retrieval heads. Then, these samples are incorporated into joint training, enabling the model to distinguish unfaithful outputs from faithful ones conditioned on control tokens."</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -726,86 +495,569 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>"Despite advancements, a significant challenge that persists is bridging the gap between user queries and documents across lexical, syntactic, semantic, and content dimensions(Zheng et al., 2020;Nogueira et al., 2019; Cheriton, 2019),termed the document-query gap."
-"However, LLMs sometimes produce false or misleading responses, also known as hallucinations."</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve"> "MEMERAG: a Multilingual End-to-end Meta-Evaluation RAG benchmark(MEMERAG). Our benchmark builds on the popular MIRACL dataset, using native language questions and generating responses with diverse large language models (LLMs), which are then assessed by expert annotators for faithfulness and relevance. " 
- "DragonBall dataset, which stands for Diverse RAG Omni-Benchmark for All scenarios"</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>"In this work, we propose UniRAG, a unified framework for query understanding in RAG. UniRAG employs a decoder only LLM to jointly perform query augmentation and encoding, eliminating task separation."
- "This backbone-agnostic efficacy highlights its ability to harmonize parametric and contextual knowledge dynamically, regardless of model architecture and context complexity."</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t xml:space="preserve"> "LongBench v2 consists of 503 challenging multiple-choice questions, with contexts ranging from 8k to 2M words, across six major task categories."
  "However, the community lacks a unified interactive framework that covers diverse environments for comprehensive evaluation of agents, and enables exploration and learning for their self-improvement. To address this, we propose AGENTGYM, a framework featuring 7 real-world scenarios, 14 environments, and 89 tasks for unified, real-time, and concurrent agent interaction."</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t xml:space="preserve"> "Agentic Reasoning dynamically leverages web search, code execution, and structured memory to address complex problems requiring deep research. A key innovation in our framework is the Mind-Map agent, which constructs a structured knowledge graph to store reasoning context and track logical relationships."
- "we propose AR-MCTS, a universal framework designed to progressively improve the reasoning capabilities of MLLMs through Active Retrieval (AR) and Monte Carlo Tree Search (MCTS)AR-MCTS follows the MCTS algorithm and heuristically integrates an active retrieval mechanism during the expansion stage to automatically acquire high-quality step-wise reasoning annotations."</t>
+    <t>RHIO框架的三个主要组成部分是什么？</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve"> "LongRefiner"使用什么特殊标签来省略冗余内容？</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>AR-MCTS算法中，为确保概念过滤的可扩展性，作者采用了什么具体策略来实现离线知识概念标注与一致性过滤？</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>作者采用开放世界标注工具 TaggerInsTag 进行离线知识概念标注，并复用前述流程执行一致性过滤，以此确保概念过滤的可扩展性。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>在构建可靠的问答（QA）系统时，这QAEncoder与On Synthesizing Data for Context Attribution in Question Answering两篇论文分别侧重于优化系统工作流的哪个阶段？它们各自试图解决的核心痛点是什么？</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>在论文"A Survey of Post-Training Scaling in Large Language Models"中，作者将post-training scaling分为哪三个主要方法？</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>首先，我们定义了“银色噪声”，它指的是仅部分包含答案的证据文本。此类噪声能够绕过大多数安全过滤机制，从而削弱 RAG 的多样性。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>" Our survey categorizes post-training scaling into three key methodologies:Supervised Fine-tuning (SFT), Reinforcement Learning from Feedback (RLxF), and Test-time Compute (TTC)."
+“The probable improving aspects include Supervised Fine-tuning (SFT), Reinforcement Learning from ‘X’ Feedback (RLxF), and Test-time Compute (TTC) (i.e., inference scaling).”
+“We categorize post-training scaling laws into three distinct stages: Supervised Fine-tuning (SFT), Reinforcement Learning (RL), and Test-time Compute (TTC).”</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>"Firstly, we define silver noise (Fig. 1-②), which refers to evidence that partially contains the answer. Such noise can circumvent most safety filters, thereby undermining the RAG diversity(R-1)."
+“To construct silver noise, which includes partial but incomplete answers, we first need to decompose the golden contexts in the base dataset.”</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>safeRAG论文, 第2页,第4页</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2025.acl-long.140_A Survey of Post-Training Scaling in Large Language Models, 第1页, 第2页,第2页</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>论文 2025.acl-long.250.pdf（NoiserBench），第1页, 第2页,第3页,第5页</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Ref-Long是一个专门设计用于评估长上下文语言模型（LCLMs）长上下文引用能力的基准。它要求LCLMs不仅要在给定文档中识别特定关键词，还要找出引用该关键词的文档索引，而不是其他相关但不匹配的文档。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve"> “Our key contribution is SYNQA: a novel generative strategy for synthesizing context attribution data. Given selected context sentences, an LLM generates QA pairs that are supported by these sentences.”
+“SYNQA produces training data that reflects the variety of real-world QA scenarios, helping models develop robust attribution capabilities.”
+“Our proposed method (SYNQA) takes a generative approach: given selected context sentences, an LLM generates question-answer pairs that are fully supported by these sentences. This approach better leverages LLMs' natural strengths in text generation while ensuring clear attribution paths in the synthetic training data.”
+"By generating both entity-centric and dialogue-centric samples, SYNQA produces training data that reflects the variety of real-world QA scenarios, helping models develop robust attribution capabilities, which our experiments demonstrate to generalize across different contexts and domains."</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>论文 2025.acl-long.828.pdf，第1页, 第2页, 第3页</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>“We propose Agentic Long-Context Understanding (AgenticLU), a framework designed to enhance an LLM's understanding of such queries by integrating targeted self-clarification with contextual grounding within an agentic workflow. At the core of AgenticLU is Chain-of-Clarifications (CoC), where models refine their understanding through self-generated clarification questions and corresponding contextual groundings.”
+“We introduce a novel framework AgenticLU to enhance long-context comprehension in LLMs. As illustrated in fig. 1, the core of AgenticLU is Chain-of-Clarifications (CoC), a process where models enhance their understanding by generating clarification questions, retrieving relevant information from the long context and answering their own clarification questions based on the gathered evidence.”
+"In this work, we introduce Agentic Long-Context Understanding (AgenticLU), a framework designed to enhance large language models' ability to process and reason over long-context inputs with self-generated data. By incorporating an agentic workflow (CoC) that dynamically refines model reasoning through self-clarifications and contextual grounding, AgenticLU significantly improves LLM's long context understanding capabilities."</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>论文 2025.acl-long.275.pdf，第1页, 第1页, 第8页</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve"> "We introduce Agentic Reasoning, a framework that enhances large language model (LLM) reasoning by integrating external tool-using agents."
+“We propose Agentic Reasoning, a streamlined framework that enhances reasoning by integrating external LLM-based agents tools.”</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2025.acl-long.1383.pdf , 第一页, 第二页</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve"> "We introduce REAL-MM-RAG, an automatically generated benchmark designed to address four key properties essential for real-world retrieval: (i) multi-modal documents, (ii) enhanced difficulty, (iii) Realistic-RAG queries and (iv) accurate labeling. Additionally, we propose a multi-difficulty-level scheme based on query rephrasing to evaluate models' semantic understanding beyond keyword matching."
+“We identify four essential properties for a real-world document retrieval benchmark, particularly in multi-modal contexts: (i) Multi-modal documents: The dataset should include pages with text, figures, tables, and other visual elements to reflect the complexity of real-world materials. (ii) Enhanced difficulty: Queries should require more than simple keyword matching and involve a large corpus of contextually similar pages to ensure challenging evaluations. (iii) Realistic-RAG queries: Questions must be posed naturally, without explicit references to pages—reflecting queries a person might ask when seeking information without knowing the answer's location (in contrast to generic question-answering setups). (iv) Accurate labeling: All documents relevant to a query must be correctly and exhaustively labeled to prevent underestimation of retrieval performance and to avoid false negatives.”</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2025.acl-long.1528.pdf , 第一页, 第一页</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>"To render LLMs resilient to imperfect retrieval, we propose ASTUTE RAG, a novel RAG approach that adaptively elicits essential information from LLMs' internal knowledge, iteratively consolidates internal and external knowledge with source-awareness, and finalizes the answer according to information reliability."
+“We propose ASTUTE RAG, which explicitly analyzes LLM-internal and external knowledge in-context, assesses their reliability, and recovers from RAG failures with black-box access.”
+“ASTUTE RAG is designed to better leverage collective knowledge from both internal knowledge of LLMs and external corpus, for more reliable responses.”</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2025.acl-long.1476_Astute RAG.pdf, 第1页, 第二页, 第五页</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>“We introduce L-CiteEval, an out-of-the-box suite that can assess both generation quality and fidelity in long-context understanding tasks. It covers 11 tasks with context lengths ranging from 8K to 48K and a corresponding automatic evaluation pipeline.”
+"To mitigate the above issues in long-context evaluation field, we propose an out-of-the-box evaluation suite, L-CiteEval, which requires LCMs to generate both the statements and their supporting evidence (citations). This suite comprises two key components: (1) a comprehensive benchmark encompassing 5 major task categories and 11 diverse long-context tasks, with context lengths ranging from 8K to 48K; and (2) corresponding automatic evaluation metrics and verification pipelines to ensure robust and reliable assessment."</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>"LongBench v2 consists of 503 challenging multiple-choice questions, with contexts ranging from 8k to 2M words, across six major task categories."
+"Length: Context length ranging from 8k to 2M words, with the majority under 128k."
+“LongBench v2 contains 503 multiple-choice questions and is made up of 6 major task categories and 20 subtasks to cover as many realistic deep comprehension scenarios as possible."</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>论文 2025.acl-long.183.pdf，第1页, 第1页, 第1页</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>RHIO框架包含三个主要组件：1.不忠实数据增强, 2.忠实度感知调优, 3.自诱导解码</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">“RHIO first augments unfaithful samples that simulate realistic model-intrinsic errors by selectively masking retrieval heads. Then, these samples are incorporated into joint training, enabling the model to distinguish unfaithful outputs from faithful ones conditioned on control tokens. Furthermore, these control tokens are leveraged to self-induce contrastive outputs, amplifying their difference through contrastive decoding.”
+"RHIO consists of three main components: unfaithful data augmentation, faithfulness-aware tuning, and self-induced decoding."
+“In this section, we introduce RHIO, a framework that enhances the contextual faithfulness of LLMs by explicitly teaching them to discriminate between faithful and unfaithful outputs, as illustrated in Figure 3. To achieve this, our approach involves augmenting realistic unfaithful samples, which enables the model to learn to distinguish faithful and unfaithful outputs conditioned on different control tokens. These control tokens are further leveraged to induce contrastive outputs and amplify the difference between them via contrastive decoding.”
+“Figure 3: An overview of RHIO: (1) unfaithful data augmentation (§3.1), which augments unfaithful output by masking out attention heads responsible for contextual faithfulness; (2) faithfulness-aware tuning (§3.2), which teaches LLMs to explicitly discriminate between faithful and unfaithful outputs; (3) self-induced decoding (§3.3), which further enhances faithfulness by amplifying the differences between induced contrastive outputs.”
+</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>论文 2025.acl-long.826.pdf, 第1页, 第15页,第3页,第4页</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>“for SFT, using only short instruction datasets yields strong performance on long-context tasks.”
+"We find that SFT with standard, short-context instruction datasets is sufficient for achieving good performance.Contrary to previous study, long synthetic instruction data does not further boost the performance."</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>论文366_How to Train Long-Context Language Models (Effectively),第1页, 第2页</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">"ASTUTE RAG first adaptively elicits LLMs' knowledge and then conducts source-aware knowledge consolidation. The desiderata is combining consistent information, identifying conflicting information, and filtering out irrelevant information."
+“To consolidate knowledge, we prompt the LLM (with pcon in Appx. A) to identify consistent information across passages, detect conflicting information between each group of consistent passages, and filter out irrelevant information.”
+</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2025.acl-long.1476_Astute RAG, 第2页,第5页</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>"Therefore, we introduce a &lt;skip&gt; tag to represent omitted content, retaining only the first and last k tokens of each paragraph while replacing the omitted content with &lt;skip&gt;."
+“The model will dynamically skip the middle portion, preserving only the first k and last k tokens, and marking the skipped portion with &lt;skip&gt;.”</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>“Another key advantage of our framework is its potential for privacy protection. Typically, when querying large- scale LLMs, local deployment is not feasible, requiring users to upload their private queries to cloud- based LLMs, raising privacy concerns. Our framework addresses this issue by enabling local SLMs to leverage the knowledge of large models while preserving user privacy."
+"With our approach, the local model first reformulates the query (much simpler than answering the query directly), stripping any sensitive information before sending it to the cloud- based model. The cloud model then retrieves relevant evidence and knowledge graphs, which are subsequently passed back to the local model for final processing and response generation. This ensures that private data remains protected while still benefiting from the power of large- scale LLMs.”
+“2) The teacher LLM is usually heavy in size and deployed on the cloud, and the student is on local devices, it is simple to develop methods for preserving privacy using our proposed framework by transmitting only de- identified queries and structured knowledge instead of full responses, as we have introduced in Section 3.3.”</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve"> 论文 2025.acl-long.358.pdf（DRAG），第5页, 第5页, 第5页</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>“In this work, we propose Self-Guided Monte Carlo Tree Search (SG-MCTS), which capitalizes on the self-reflection capability of LLMs to guide the search process of MCTS."
+"In each iteration, SG-MCTS follows four steps, i.e., selection, reflection-guided expansion, evaluation, and backpropagation."</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>论文 2025.acl-long.490.pdf（Think&amp; Cite），第3页, 第4页</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>"To address the aforementioned challenges, we propose transforming the RDF graph into multiple domain-specific property graphs and using Cypher to query them."
+"In this section, we introduce our approach for transforming RDF, specifically Wikidata, into property graphs as the initial step in building CypherBench."</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2025.acl-long.438.pdf , 第4页, 第4页</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>QAEncoder如何解决文档-查询差距问题？</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>QAEncoder采用了一种无需训练的方法来弥合文档与查询之间的差距。其核心机制包含两点：
+潜在查询期望估计： 在嵌入空间中估计潜在查询的期望值，将其作为文档嵌入的鲁棒替代表示，从而使文档表示在语义上更贴近查询空间。
+文档指纹附加： 为这些嵌入表示附加文档指纹，以有效区分不同文档的嵌入，避免仅依赖查询期望导致的文档辨识度丢失问题。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2025.acl-long.1574_CiteEval , 第8页</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>RankCoT 模型相较于原始 RAG 模型的具体优势体现在以下两方面：
+量化性能提升：实验结果显示，RankCoT 的性能比原始 RAG 模型提高了 2.5%。
+优化机制优势：该模型能够提供更有效的精炼信息，从而帮助大语言模型更好地回答问题。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>"We employ both automated and manual review processes to maintain high quality and difficulty, resulting in human experts achieving only 53.7% accuracy under a 15-minute time constraint."
+"Human experts are able to achieve an accuracy of 53.7% within 15 minutes, compared to 25% accuracy with random guessing, highlighting the challenging nature of the test."</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve"> 论文 2025.acl-long.183.pdf，第1页, 第2页</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>"For instance, agents with AGENTSTAR outperform GPT-4-Turbo and AGENTTRAJ-L-SFT by 61.00 and 3.00 points on WebShop (Yao et al., 2022), 20.50 and 5.00 points on ALFWorld (Shridhar et al., 2021), and 9.87 and 8.51 points on BabyAI (Chevalier-Boisvert et al., 2019). This validates the superiority and promise of the exploration and learning paradigm in developing agents (Zelikman et al., 2022)."</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>AGENTSTAR方法在WebShop、ALFWorld和BabyAI任务上与GPT-4-Turbo相比有何优势？</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>AGENTSTAR 在这三个任务上的性能全面超越了 GPT-4-Turbo。其中在 WebShop 上的提升最为显著（远超 GPT-4-Turbo 61 个百分点），在 ALFWorld 和 BabyAI 上也分别实现了大幅领先（超过 GPT-4-Turbo 20.5 和 9.87 个百分点）。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>"On GAIA(as shown in Table 3), Agentic Reasoning establishes a new SOTA among all publicly available methods. Compared to OpenAI's Deep Research, which leverages its proprietary high-performance reasoning models, our approach surpasses it on Level 1 and Level 2 tasks while narrowing the gap to 2.26% on Level 3."</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>《Astute RAG》：采用自适应段落生成机制，通过提示大模型直接生成包含内部知识的段落，并允许模型自适应决定生成的段落数量。
+《FaithfulRAG》：采用自我事实挖掘 模块，通过外部化大模型对问题的理解，提取出细粒度的、事实级别的内部知识。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>"FaithfulRAG adopts a novel self-fact mining module to externalize the LLM’s understanding of the question, obtaining fine-grained knowledge at the fact level."
+"Our approach addresses both aspects by employing a hierarchical,three-stage process that externalizes the model’s internal knowledge into distinct logical and fine-grained factual representations.Specifically, for a given question Q, our objective is to extract the essential factual and conceptual information required to answer Q while filtering out unnecessary details. We achieve this through the following three sequential stages: Self Knowledge Extraction,Self-Context Generation and Self-Fact Extraction."
+"To achieve this goal, we enhance the original method with constitutional principles and adaptive generatio.n"
+"Moreover, we allow the LLM to perform adaptive generation of passages in its internal knowledge. The LLM can decide how many passages to generate by itself."</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>《FaithfulRAG》,第2页
+《FaithfulRAG》,第4页
+《Astute RAG》, 第5页
+《Astute RAG》, 第5页</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>UniRAG提出统一的查询理解框架，集成查询增强和查询编码两个阶段；FaithfulRAG通过自我事实挖掘和自思考模块，在事实级别识别并解决参数化知识与检索上下文之间的冲突，提高语义一致性。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>"In this work, we propose UniRAG, a unified framework for query understanding in RAG. UniRAG employs a decoder only LLM to jointly perform query augmentation and encoding, eliminating task separation."
+"To address these challenges, this work introduces UniRAG. As shown on the right side of Figure 1, we achieve unified execution of query augmentation and query encoding by training a decoder</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Cambria Math"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t>‑</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>only LLM."
+"FaithfulRAG identifies conflicting knowledge at the fact level and designs a self</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Cambria Math"/>
+        <family val="1"/>
+        <charset val="1"/>
+      </rPr>
+      <t>‑</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>thinking process, allowing LLMs to reason about and integrate conflicting facts before generating responses."
+"FaithfulRAG adopts a novel self</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Cambria Math"/>
+        <family val="1"/>
+        <charset val="1"/>
+      </rPr>
+      <t>‑</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>fact mining module to externalize the LLM's understanding of the question, obtaining fine</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Cambria Math"/>
+        <family val="1"/>
+        <charset val="1"/>
+      </rPr>
+      <t>‑</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>grained knowledge at the fact level."
+"FaithfulRAG first designs a self-fact mining module to externalize the LLM’s understanding of the question, obtaining fine-grained knowledge at the fact level. Then itidentifies conflicting knowledge by aligning self-fact with the retrieved contexts and adopts a self-thinking module,allowing LLMs to reason about and integrate conflicting facts before generating responses."</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2025.acl-long.693_UniRAG , 第1页, 第1页 ;  2025.acl-long.1062_FaithfulRAG , 第1页, 第2页, 第4页</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve"> 论文 2025.acl-long.1101.pdf(MEMERAG), 第1页, 第3页; 2025.acl-long.418.pdf(DragonBall), 第4页, 第5页</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>" Our dataset encompasses 5 languages: English (EN), German (DE), Spanish (ES), French(FR), and Hindi (HI), which represent multiple language families and both high- and low-resource languages."
+“Our benchmark builds on the popular MIRACL dataset, using native-language questions and generating responses with diverse LLMs, which are then assessed by expert annotators for faithfulness and relevance.”
+ “We construct the DragonBall dataset, which stands for Diverse RAG Omni-Benchmark for All scenarios,  by leveraging the generation method described above." 
+" In addition, the dataset features both Chinese and English texts,serving as a comprehensive resource for multilingual, scenario-specific research."</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>"Our key contribution is SYNQA: a novel generative strategy for synthesizing context attribution data."
+"We show that the attribution data synthesized via SYNQA is highly effective for fine-tuning small LMs for context attribution in different QA tasks and domains"
+"RHIO first augments unfaithful samples that simulate realistic model-intrinsic errors by selectively masking retrieval heads. Then, these samples are incorporated into joint training, enabling the model to distinguish unfaithful outputs from faithful ones conditioned on control tokens."
+“This finding motivates us to generate more realistic unfaithful outputs by simply masking out retrieval heads of LLMs.”</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SYNQA: 2025.acl-long.828.pdf，第1页, 第1页
+RHIO: 2025.acl-long.826.pdf，第1页, 第3页</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Agentic Reasoning - 2025.acl-long.1383.pdf , 第1页, 第2页；AR-MCTS - 2025.acl-long.180.pdf , 第1页, 第2页</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve"> "Agentic Reasoning dynamically leverages web search, code execution, and structured memory to address complex problems requiring deep research. A key innovation in our framework is the Mind-Map agent, which constructs a structured knowledge graph to store reasoning context and track logical relationships."
+"In the overall process, we deploy a Web</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Cambria Math"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t>‑</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Search agent and a Code agent as problem</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Cambria Math"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t>‑</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>solving tools, along with a knowledge</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Cambria Math"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t>‑</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>graph agent, called Mind</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Cambria Math"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t>‑</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Map, to serve as memory."
+" In this paper, we propose AR-MCTS, a universal framework designed to progressively improve the reasoning capabilities of MLLMs through Active Retrieval (AR) and Monte Carlo Tree Search (MCTS). AR-MCTS follows the MCTS algorithm and heuristically integrates an active retrieval mechanism during the expansion stage to automatically acquire high‑quality step‑wise reasoning annotations."
+"We propose AR</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Cambria Math"/>
+        <family val="1"/>
+        <charset val="1"/>
+      </rPr>
+      <t>‑</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>MCTS, a universal framework dedicated to progressively improving the complex reasoning capabilities of MLLMs through Active Retrieval and Monte Carlo Tree Search."</t>
+    </r>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t xml:space="preserve"> "We introduce REAL-MM-RAG, an automatically generated benchmark designed to address four key properties essential for real-world retrieval: (i) multi-modal documents, (ii) enhanced difficulty, (iii) Realistic-RAG queries and (iv) accurate labeling."
+"We identify four essential properties for a real-world document retrieval benchmark, particularly in multi-modal contexts: (i) Multi-modal documents: The dataset should include pages with text, figures, tables, and other visual elements to reflect the complexity of real-world materials. (ii)Enhanced difficulty: Queries should require more than simple keyword matching and involve a large corpus of contextually similar pages to ensure challenging evaluations. (iii) Realistic-RAG queries:Questions must be posed naturally, without explicit references to pages—reflecting queries a person might ask when seeking information without knowing the answer’s location (in contrast to generic question-answering setups). (iv) Accurate labeling: All documents relevant to a query must be correctly and exhaustively labeled to prevent underestimation of retrieval performance and to avoid false negatives"
 "Firstly, each question-answering pair can be categorized by three primary tasks: Understanding, Reasoning, and Locating, as discussed in Section 1. Secondly, we define four types of answer evidences based on element type: (1) Text: pure texts, such as paragraph; (2) Layout: text elements with special layout meaning (generalized text), such as title, header, footer, table name and figure name; (3) Figure: including charts and general images. (4) Table. In addition, each question-answering pair can be classified into single-page or multi-page based on the number of answer evidence pages and single element or cross-element based on the number of types of evidence elements. Based on different primary tasks and answer evidences, we divide our dataset into 20 sub-tasks."</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>"The teacher LLM is usually heavy in size and deployed on the cloud, and the student is on local devices. It is simple to develop methods for preserving privacy using our proposed framework by transmitting only de-identified queries and structured knowledge instead of full responses, as we have introduced in Section 3.3."</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>"we propose Self-Guided Monte Carlo Tree Search (SG-MCTS), which capitalizes on the self-reflection capability of LLMs to reason about the intermediate states of MCTS for guiding the tree expansion process." 
-"In each iteration, SG-MCTS follows four steps, i.e., selection, reflection-guided expansion, evaluation, and backpropagation."</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>RHIO框架的三个主要组成部分是什么？</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>RHIO框架包含三个主要组件：
-1.不忠实数据增强（Unfaithful Data Augmentation）
-2.忠实度感知调优（Faithfulness-Aware Tuning）
-3.自诱导解码（Self-Induced Decoding）</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">"RHIO consists of three main components: unfaithful data augmentation, faithfulness-aware tuning, and self-induced decoding."
+    <t>REAL-MM-RAG - 2025.acl-long.1528.pdf , 第1页, 第1页；LongDocURL - 2025.acl-long.57.pdf (第4页)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>“However, the inherent gap between user queries and relevant documents hinders precise matching. We introduce QAEncoder, a training</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Cambria Math"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t>‑</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">free approach to bridge this gap.”
+"Despite advancements, a significant challenge that persists is bridging the gap between user queries and documents across lexical, syntactic, semantic, and content dimensions(Zheng et al., 2020;Nogueira et al., 2019; Cheriton, 2019),termed the document-query gap."
+“However, LLMs sometimes produce false or misleading responses, also known as hallucinations. Therefore, grounding the generated answers in contextually provided information i.e., providing evidence for the generated text is paramount for LLMs' trustworthiness. Providing this information is the task of context attribution.”
+“This poses the need for context attribution methods that create links between the answer and different relevant parts of the (potentially large) reference text.”
 </t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve"> "LongRefiner"使用什么特殊标签来省略冗余内容？</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>"Since most tokens in the flat representation are derived from the original document, we can omit redundant content and restore it during structure recovery. Therefore, we introduce a &lt;skip&gt; tag to represent omitted content, retaining only the first and last k tokens of each paragraph while replacing the omitted content with &lt;skip&gt;."</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>AR-MCTS算法中，为确保概念过滤的可扩展性，作者采用了什么具体策略来实现离线知识概念标注与一致性过滤？</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>作者采用开放世界标注工具 TaggerInsTag 进行离线知识概念标注，并复用前述流程执行一致性过滤，以此确保概念过滤的可扩展性。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>在构建可靠的问答（QA）系统时，这QAEncoder与On Synthesizing Data for Context Attribution in Question Answering两篇论文分别侧重于优化系统工作流的哪个阶段？它们各自试图解决的核心痛点是什么？</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>" Our survey categorizes post-training scaling into three key methodologies:Supervised Fine-tuning (SFT), Reinforcement Learning from Feedback (RLxF), and Test-time Compute (TTC)."</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>2025.acl-long.140_A Survey of Post-Training Scaling in Large Language Models, 第1页</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2025.acl-long.217_QAEncoder.pdf, 第1页, 第1页; 2025.acl-long.828_On Synthesizing Data for Context Attribution in Question Answering, 第1页, 第1页</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>"Through empirical evaluation of eight representative LLMs with diverse architectures and scales, we reveal that these noises can be further categorized into two practical groups: noise that is beneficial to LLMs(aka beneficial noise) and noise that is harmful to LLMs (aka harmful noise)."
+“We define seven types of noise and categorize them into two groups: beneficial and harmful noise.”
+“As shown in Figure 2, we categorize RAG noise into seven linguistic types. They are further divided into beneficial (semantic, datatype, and illegal sentence) and harmful noise (counterfactual, supportive, orthographic, and prior) for practical applications.”
+“Based on these trends, we can categorize retrieval noises into two types: harmful noise (counterfactual, supportive, and orthographic) and beneficial noise (semantic, datatype, and illegal sentence).”</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">“To bridge this gap, this paper proposes Referencing Evaluation for Long-context Language Models (Ref-Long), a novel benchmark designed to assess the long-context referencing capability of LCLMs.Specifically, Ref-Long requires LCLMs to identify the indexes of documents that reference a specific key, emphasizing contextual relationships between the key and the documents over simple retrieval.”
+</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>论文 2025.acl-long.1162.pdf（Ref-Long），第1页</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve"> 什么是SYNQA方法？</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve"> SYNQA是一种生成合成训练数据的方法，用于训练上下文归因模型。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>作者将post-training scaling分为三个主要方法：Supervised Fine-tuning (SFT), Reinforcement Learning (RLxF), and Test-time Compute (TTC).</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -813,7 +1065,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -843,6 +1095,20 @@
       <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Cambria Math"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Cambria Math"/>
+      <family val="1"/>
+      <charset val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -1183,172 +1449,172 @@
         <v>14</v>
       </c>
     </row>
-    <row r="2" spans="1:4" ht="56" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:4" ht="168" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
-        <v>72</v>
+        <v>116</v>
       </c>
       <c r="B2" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" ht="98" x14ac:dyDescent="0.3">
+      <c r="A3" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="D3" s="1" t="s">
         <v>120</v>
       </c>
-      <c r="C2" s="1" t="s">
-        <v>180</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" ht="84" x14ac:dyDescent="0.3">
-      <c r="A3" s="1" t="s">
-        <v>121</v>
-      </c>
-      <c r="B3" s="1" t="s">
+    </row>
+    <row r="4" spans="1:4" ht="238" x14ac:dyDescent="0.3">
+      <c r="A4" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="D4" s="1" t="s">
         <v>122</v>
       </c>
-      <c r="C3" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" ht="84" x14ac:dyDescent="0.3">
-      <c r="A4" s="1" t="s">
-        <v>119</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>118</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>130</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" ht="112" x14ac:dyDescent="0.3">
+    </row>
+    <row r="5" spans="1:4" ht="140" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
         <v>18</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>19</v>
+        <v>123</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>20</v>
+        <v>178</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" ht="84" x14ac:dyDescent="0.3">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" ht="280" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" ht="364" x14ac:dyDescent="0.3">
+      <c r="A7" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="B6" s="1" t="s">
+      <c r="B7" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="C6" s="1" t="s">
+      <c r="C7" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" ht="84" x14ac:dyDescent="0.3">
+      <c r="A8" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" ht="378" x14ac:dyDescent="0.3">
+      <c r="A9" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" ht="210" x14ac:dyDescent="0.3">
+      <c r="A10" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" ht="224" x14ac:dyDescent="0.3">
+      <c r="A11" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="D11" s="4" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" ht="126" x14ac:dyDescent="0.3">
+      <c r="A12" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D6" s="1" t="s">
+      <c r="B12" s="1" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="7" spans="1:4" ht="126" x14ac:dyDescent="0.3">
-      <c r="A7" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" ht="42" x14ac:dyDescent="0.3">
-      <c r="A8" s="3" t="s">
-        <v>133</v>
-      </c>
-      <c r="B8" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>132</v>
-      </c>
-      <c r="D8" s="3" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" ht="126" x14ac:dyDescent="0.3">
-      <c r="A9" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="B9" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="D9" s="3" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" ht="98" x14ac:dyDescent="0.3">
-      <c r="A10" s="3" t="s">
+      <c r="C12" s="1" t="s">
         <v>135</v>
       </c>
-      <c r="B10" s="3" t="s">
-        <v>134</v>
-      </c>
-      <c r="C10" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="D10" s="3" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" ht="154" x14ac:dyDescent="0.3">
-      <c r="A11" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="B11" s="3" t="s">
-        <v>96</v>
-      </c>
-      <c r="C11" s="3" t="s">
-        <v>97</v>
-      </c>
-      <c r="D11" s="4" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" ht="42" x14ac:dyDescent="0.3">
-      <c r="A12" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="C12" s="1" t="s">
-        <v>38</v>
-      </c>
       <c r="D12" s="1" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" ht="56" x14ac:dyDescent="0.3">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" ht="409.5" x14ac:dyDescent="0.3">
       <c r="A13" s="1" t="s">
-        <v>172</v>
+        <v>111</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>173</v>
+        <v>137</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>174</v>
+        <v>138</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>84</v>
+        <v>139</v>
       </c>
     </row>
   </sheetData>
@@ -1383,158 +1649,158 @@
         <v>14</v>
       </c>
     </row>
-    <row r="2" spans="1:4" ht="98" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:4" ht="126" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
-        <v>76</v>
+        <v>56</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>77</v>
+        <v>57</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" ht="112" x14ac:dyDescent="0.3">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" ht="182" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>3</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>126</v>
+        <v>84</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>127</v>
+        <v>142</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>74</v>
+        <v>143</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="112" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
-        <v>175</v>
+        <v>112</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>176</v>
+        <v>144</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" ht="112" x14ac:dyDescent="0.3">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" ht="392" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
         <v>15</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>82</v>
+        <v>59</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>170</v>
+        <v>145</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" ht="112" x14ac:dyDescent="0.3">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" ht="98" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
-        <v>138</v>
+        <v>91</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>137</v>
+        <v>90</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>171</v>
+        <v>147</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>139</v>
+        <v>148</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="154" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
-        <v>140</v>
+        <v>92</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>141</v>
+        <v>93</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>142</v>
+        <v>94</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>143</v>
+        <v>95</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="126" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
-        <v>46</v>
+        <v>33</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>47</v>
+        <v>34</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>48</v>
+        <v>35</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>128</v>
+        <v>85</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="70" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
-        <v>177</v>
+        <v>113</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>178</v>
+        <v>114</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>85</v>
+        <v>60</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" ht="56" x14ac:dyDescent="0.3">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" ht="112" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
-        <v>144</v>
+        <v>96</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>145</v>
+        <v>97</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>87</v>
+        <v>150</v>
       </c>
     </row>
     <row r="11" spans="1:4" ht="210" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="s">
-        <v>63</v>
+        <v>47</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>64</v>
+        <v>48</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>65</v>
+        <v>49</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>88</v>
+        <v>62</v>
       </c>
     </row>
     <row r="12" spans="1:4" ht="154" x14ac:dyDescent="0.3">
       <c r="A12" s="1" t="s">
-        <v>69</v>
+        <v>151</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>90</v>
+        <v>152</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>124</v>
+        <v>82</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>89</v>
+        <v>63</v>
       </c>
     </row>
   </sheetData>
@@ -1578,7 +1844,7 @@
         <v>6</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>79</v>
+        <v>153</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="56" x14ac:dyDescent="0.3">
@@ -1592,133 +1858,133 @@
         <v>11</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" ht="98" x14ac:dyDescent="0.3">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" ht="84" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
-        <v>147</v>
+        <v>98</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>148</v>
+        <v>154</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>94</v>
+        <v>65</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>93</v>
+        <v>64</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="70" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
-        <v>153</v>
+        <v>103</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>154</v>
+        <v>104</v>
       </c>
       <c r="C5" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" ht="126" x14ac:dyDescent="0.3">
+      <c r="A6" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="D5" s="1" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" ht="70" x14ac:dyDescent="0.3">
-      <c r="A6" s="1" t="s">
-        <v>40</v>
-      </c>
       <c r="B6" s="1" t="s">
-        <v>41</v>
+        <v>30</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>42</v>
+        <v>155</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" ht="266" x14ac:dyDescent="0.3">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" ht="140" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
-        <v>100</v>
+        <v>158</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>101</v>
+        <v>159</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>102</v>
+        <v>157</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>103</v>
+        <v>70</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="70" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
-        <v>51</v>
+        <v>38</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>52</v>
+        <v>39</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>53</v>
+        <v>40</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" ht="98" x14ac:dyDescent="0.3">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" ht="112" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
-        <v>54</v>
+        <v>41</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>105</v>
+        <v>72</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>55</v>
+        <v>160</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>104</v>
+        <v>71</v>
       </c>
     </row>
     <row r="10" spans="1:4" ht="140" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
-        <v>60</v>
+        <v>44</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>61</v>
+        <v>45</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>62</v>
+        <v>46</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>106</v>
+        <v>73</v>
       </c>
     </row>
     <row r="11" spans="1:4" ht="168" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="s">
-        <v>107</v>
+        <v>74</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>68</v>
+        <v>52</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>125</v>
+        <v>83</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>108</v>
+        <v>75</v>
       </c>
     </row>
     <row r="12" spans="1:4" ht="98" x14ac:dyDescent="0.3">
       <c r="A12" s="1" t="s">
-        <v>150</v>
+        <v>100</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>149</v>
+        <v>99</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>151</v>
+        <v>101</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>152</v>
+        <v>102</v>
       </c>
     </row>
   </sheetData>
@@ -1751,116 +2017,116 @@
         <v>14</v>
       </c>
     </row>
-    <row r="2" spans="1:4" ht="112" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:4" ht="266" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
-        <v>155</v>
+        <v>105</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>156</v>
+        <v>161</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>157</v>
+        <v>162</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" ht="126" x14ac:dyDescent="0.3">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" ht="409.5" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>8</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>81</v>
+        <v>164</v>
       </c>
       <c r="C3" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="D3" s="1" t="s">
         <v>166</v>
       </c>
-      <c r="D3" s="1" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" ht="126" x14ac:dyDescent="0.3">
+    </row>
+    <row r="4" spans="1:4" ht="196" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>109</v>
+        <v>76</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" ht="126" x14ac:dyDescent="0.3">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" ht="196" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>160</v>
+        <v>106</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>159</v>
+        <v>169</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>111</v>
+        <v>170</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="154" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
-        <v>161</v>
+        <v>107</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>44</v>
+        <v>31</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>167</v>
+        <v>110</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" ht="182" x14ac:dyDescent="0.3">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" ht="409.5" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
-        <v>66</v>
+        <v>50</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>116</v>
+        <v>78</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" ht="280" x14ac:dyDescent="0.3">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" ht="409.5" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
-        <v>162</v>
+        <v>108</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>67</v>
+        <v>51</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="D8" s="1" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" ht="365.5" x14ac:dyDescent="0.3">
+      <c r="A9" s="1" t="s">
         <v>115</v>
       </c>
-    </row>
-    <row r="9" spans="1:4" ht="126" x14ac:dyDescent="0.3">
-      <c r="A9" s="1" t="s">
-        <v>179</v>
-      </c>
       <c r="B9" s="1" t="s">
-        <v>163</v>
+        <v>109</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>164</v>
+        <v>175</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>113</v>
+        <v>176</v>
       </c>
     </row>
   </sheetData>
@@ -1897,13 +2163,13 @@
         <v>12</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>129</v>
+        <v>86</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="28" x14ac:dyDescent="0.3">
@@ -1911,13 +2177,13 @@
         <v>13</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>129</v>
+        <v>86</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="28" x14ac:dyDescent="0.3">
@@ -1925,10 +2191,10 @@
         <v>16</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>129</v>
+        <v>86</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>17</v>
@@ -1936,72 +2202,72 @@
     </row>
     <row r="5" spans="1:4" ht="42" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>129</v>
+        <v>86</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="28" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>129</v>
+        <v>86</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="28" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
-        <v>45</v>
+        <v>32</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>129</v>
+        <v>86</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="28" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
-        <v>70</v>
+        <v>53</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>129</v>
+        <v>86</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="28" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
-        <v>71</v>
+        <v>54</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>129</v>
+        <v>86</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
     </row>
   </sheetData>

--- a/code/测试集.xlsx
+++ b/code/测试集.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\rag_project\code\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{15C65696-AF9F-46D4-99FB-E135E66EF3B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A32E49B-9175-4E45-981A-4465514C711F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -70,10 +70,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>&lt;skip&gt;标签，用于表示省略的内容，只保留每个段落的前k个和后k个token。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>"UniRAG"和"FaithfulRAG"在处理查询理解方面的核心创新分别是什么？</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -106,10 +102,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>SETR模型在训练时使用了多少个GPU？具体的训练时间是多少小时？</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t xml:space="preserve"> 无</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -134,19 +126,11 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>比较SYNQA和RHIO两种方法在提升模型性能方面的不同策略。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>论文中是否提到了SYNQA方法在医疗领域的具体应用案例？</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>什么是Agentic Long-Context Understanding (AgenticLU)框架？</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve"> AgenticLU是一个旨在增强大语言模型处理和推理长上下文输入能力的框架。它通过结合代理工作流（Chain-of-Clarifications），通过自我澄清和上下文锚定动态优化模型推理，显著提高LLM的长上下文理解能力。</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -179,10 +163,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>α参数的最优范围在0.65到0.8之间。这个参数用于平衡工具描述和参数描述在工具检索中的权重，其中工具描述起相对更重要的作用。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>"As the value of α increases, the hit rate initially rises and then declines, reaching its optimal range when α is between 0.65 and 0.8. These findings confirm that incorporating parameter descriptions does not degrade the performance of tool retrieval. Instead, it enhances the overall effectiveness of the retrieval process when appropriately balanced with tool descriptions."</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -195,10 +175,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>在Humanity's Last Exam数据集上，Agentic Reasoning与DeepSeek-R1结合的性能提升是多少？</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>在Humanity's Last Exam数据集上，Agentic Reasoning与DeepSeek-R1结合达到了23.8%的准确率，比基础模型提升了14.4%，与专有的OpenAI Deep Research的差距缩小到仅2.8%。</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -211,14 +187,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t xml:space="preserve"> REAL-MM-RAG基准测试的四个关键属性是什么？</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve"> REAL-MM-RAG基准测试的四个关键属性是：(i) 多模态文档，(ii) 增强的难度，(iii) 真实的RAG查询，(iv) 准确的标注。此外，该基准还提出了基于查询改写的多难度级别方案，以评估模型超越关键词匹配的语义理解能力。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t xml:space="preserve"> 在Asclepius医学基准测试中，人类医生与Med-MLLMs的表现对比如何？</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -227,10 +195,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t xml:space="preserve"> "Human physicians surpass Med-MLLMs in diagnostic accuracy across all specialties. Even a junior doctor with an average accuracy of 57.4%, marginally exceeds the most proficient Med-MLLM, GPT-4V, which achieved an accuracy of 54.3%. This outcome suggests that, despite the advancements made in artificial intelligence, there is still a gap in diagnostic precision between human expertise and current Med-MLLMs."</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t xml:space="preserve"> ClinRaGen框架的三阶段理由蒸馏范式是什么？</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -243,14 +207,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>比较Agentic Reasoning和AR-MCTS在处理复杂推理任务时的方法差异。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>REAL-MM-RAG专注于真实世界的多模态文档检索，强调四个关键属性：多模态文档、增强难度、真实RAG查询和准确标注，并使用基于查询改写的多难度级别方案。LongDocURL则专注于长文档理解，将问题分为理解、推理和定位三类任务，并根据证据元素类型（文本、布局、图表、表格）和页面数量（单页、多页、跨元素）进行细分，共20个子任务。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>在LongDocURL基准测试中，只有GPT-4o达到了及格标准，得分为64.5，表明该基准对当前模型提出了重大挑战。在开源模型中，只有Qwen2-VL（得分30.6）和LLaVA-OneVision（得分22.0和25.0）超过了20分的阈值，其他参数少于13B的模型都低于这个阈值。</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -263,10 +219,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>2025.acl-long.176_Hierarchical Document Refinement for Long-context Retrieval-augmented Generation ,第四页</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>在论文《How to Train Long-Context Language Models (Effectively)》中，作者在进行监督微调（SFT）阶段时，对于长上下文模型的指令微调数据选择得出了什么反直觉的结论？</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -283,15 +235,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t xml:space="preserve"> "To ensure the scalability of concept filtering, we use the open-world TaggerInsTag (Lu et al., 2024a) for offline knowledge concept annotation and repeat the aforementioned
-process for consistency filtering."</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve"> 2025.acl-long.180.pdf (第22页)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>2025.acl-long.540.pdf (第4页)</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -333,10 +276,6 @@
   </si>
   <si>
     <t>在GAIA基准测试中，Agentic Reasoning在Level 1和Level 2任务上超越了OpenAI的Deep Research，在Level 3任务上将差距缩小到2.26%。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>2025.acl-long.1178.pdf (第7页)</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -357,19 +296,7 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>Agentic Reasoning通过动态利用网络搜索、代码执行和结构化记忆来解决复杂问题，核心创新是Mind-Map agent构建知识图存储推理上下文。而AR-MCTS通过主动检索（AR）和蒙特卡洛树搜索（MCTS）逐步提升多模态大语言模型（MLLM）的推理能力，该框架遵循MCTS算法并在扩展阶段启发式地集成主动检索机制，以自动获取高质量的逐步推理注释。两者都使用外部工具增强推理，但Agentic Reasoning更注重工具集成和记忆管理，AR-MCTS更注重搜索策略和状态评估。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>RAG噪声被分为有益噪声（beneficial noise）和有害噪声（harmful noise）。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>RAG噪声被分为哪两类？</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>在"safeRAG"论文中，作者定义的"silver noise"指什么？</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -412,10 +339,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t xml:space="preserve"> Think&amp; Cite框架中的Self-Guided Monte Carlo Tree Search (SG-MCTS)如何工作？有几个步骤?</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>SETR 的段落选择提示（Passage Selection Prompt）所引导的关键过程包含哪三个具体步骤？每个步骤的核心任务是什么？</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -443,26 +366,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>根据实验结果，RankCoT 模型相较于原始 RAG 模型有哪些具体优势？</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>实验结果表明，RAGEval 的机器自动评估与人工评估在所有指标上均表现出高度一致性。两者之间的最终绝对差异仅为 1.67%，且三位标注者之间的 Fleiss’ Kappa 值达到了 0.7686，验证了该自动评估指标的可靠性及其与人类判断的一致性。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>RAGEval 提出的自动评估指标与人工评估的一致性如何？</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>"Results in Figure 7 show that the machine and human evaluations show a high degree of alignment in all metrics. The final absolute difference between the human evaluation and the machine evaluation is 1.67%. The Fleiss’ Kappa value between the three annotators is 0.7686."</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>2025.acl-long.418_RAGEval.pdf, 第11页</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>在 HALoGEN 基准测试中，表现最好的 LLM 生成事实的幻觉率范围是多少？</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -475,16 +378,7 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>SYNQA：通过 SYNQA 合成的训练数据在对小型语言模型进行微调以实现不同问答任务和领域的上下文归因时非常有效;
-RHIO：负向数据增强与错误模拟。通过选择性地掩码检索头，故意制造出“不忠实”的样本，以模拟模型在真实情况下的内在错误, 然后将正常样本与这些构造出的错误样本放在一起进行联合训练，并引入“控制标记”。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>比较LongBench v2和AGENTGYM应用场景区别。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>比较LongDocURL与REAL-MM-RAG这两个基准测试在构建评估体系（或任务设计）时的侧重点差异</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -504,18 +398,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t xml:space="preserve"> "LongRefiner"使用什么特殊标签来省略冗余内容？</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>AR-MCTS算法中，为确保概念过滤的可扩展性，作者采用了什么具体策略来实现离线知识概念标注与一致性过滤？</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>作者采用开放世界标注工具 TaggerInsTag 进行离线知识概念标注，并复用前述流程执行一致性过滤，以此确保概念过滤的可扩展性。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>在构建可靠的问答（QA）系统时，这QAEncoder与On Synthesizing Data for Context Attribution in Question Answering两篇论文分别侧重于优化系统工作流的哪个阶段？它们各自试图解决的核心痛点是什么？</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -544,10 +426,6 @@
   </si>
   <si>
     <t>2025.acl-long.140_A Survey of Post-Training Scaling in Large Language Models, 第1页, 第2页,第2页</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>论文 2025.acl-long.250.pdf（NoiserBench），第1页, 第2页,第3页,第5页</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -559,10 +437,6 @@
 “SYNQA produces training data that reflects the variety of real-world QA scenarios, helping models develop robust attribution capabilities.”
 “Our proposed method (SYNQA) takes a generative approach: given selected context sentences, an LLM generates question-answer pairs that are fully supported by these sentences. This approach better leverages LLMs' natural strengths in text generation while ensuring clear attribution paths in the synthetic training data.”
 "By generating both entity-centric and dialogue-centric samples, SYNQA produces training data that reflects the variety of real-world QA scenarios, helping models develop robust attribution capabilities, which our experiments demonstrate to generalize across different contexts and domains."</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>论文 2025.acl-long.828.pdf，第1页, 第2页, 第3页</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -635,15 +509,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>“for SFT, using only short instruction datasets yields strong performance on long-context tasks.”
-"We find that SFT with standard, short-context instruction datasets is sufficient for achieving good performance.Contrary to previous study, long synthetic instruction data does not further boost the performance."</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>论文366_How to Train Long-Context Language Models (Effectively),第1页, 第2页</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t xml:space="preserve">"ASTUTE RAG first adaptively elicits LLMs' knowledge and then conducts source-aware knowledge consolidation. The desiderata is combining consistent information, identifying conflicting information, and filtering out irrelevant information."
 “To consolidate knowledge, we prompt the LLM (with pcon in Appx. A) to identify consistent information across passages, detect conflicting information between each group of consistent passages, and filter out irrelevant information.”
 </t>
@@ -654,11 +519,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>"Therefore, we introduce a &lt;skip&gt; tag to represent omitted content, retaining only the first and last k tokens of each paragraph while replacing the omitted content with &lt;skip&gt;."
-“The model will dynamically skip the middle portion, preserving only the first k and last k tokens, and marking the skipped portion with &lt;skip&gt;.”</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>“Another key advantage of our framework is its potential for privacy protection. Typically, when querying large- scale LLMs, local deployment is not feasible, requiring users to upload their private queries to cloud- based LLMs, raising privacy concerns. Our framework addresses this issue by enabling local SLMs to leverage the knowledge of large models while preserving user privacy."
 "With our approach, the local model first reformulates the query (much simpler than answering the query directly), stripping any sensitive information before sending it to the cloud- based model. The cloud model then retrieves relevant evidence and knowledge graphs, which are subsequently passed back to the local model for final processing and response generation. This ensures that private data remains protected while still benefiting from the power of large- scale LLMs.”
 “2) The teacher LLM is usually heavy in size and deployed on the cloud, and the student is on local devices, it is simple to develop methods for preserving privacy using our proposed framework by transmitting only de- identified queries and structured knowledge instead of full responses, as we have introduced in Section 3.3.”</t>
@@ -698,12 +558,6 @@
   </si>
   <si>
     <t>2025.acl-long.1574_CiteEval , 第8页</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>RankCoT 模型相较于原始 RAG 模型的具体优势体现在以下两方面：
-量化性能提升：实验结果显示，RankCoT 的性能比原始 RAG 模型提高了 2.5%。
-优化机制优势：该模型能够提供更有效的精炼信息，从而帮助大语言模型更好地回答问题。</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -852,10 +706,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t xml:space="preserve"> 论文 2025.acl-long.1101.pdf(MEMERAG), 第1页, 第3页; 2025.acl-long.418.pdf(DragonBall), 第4页, 第5页</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>" Our dataset encompasses 5 languages: English (EN), German (DE), Spanish (ES), French(FR), and Hindi (HI), which represent multiple language families and both high- and low-resource languages."
 “Our benchmark builds on the popular MIRACL dataset, using native-language questions and generating responses with diverse LLMs, which are then assessed by expert annotators for faithfulness and relevance.”
  “We construct the DragonBall dataset, which stands for Diverse RAG Omni-Benchmark for All scenarios,  by leveraging the generation method described above." 
@@ -876,126 +726,6 @@
   </si>
   <si>
     <t>Agentic Reasoning - 2025.acl-long.1383.pdf , 第1页, 第2页；AR-MCTS - 2025.acl-long.180.pdf , 第1页, 第2页</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve"> "Agentic Reasoning dynamically leverages web search, code execution, and structured memory to address complex problems requiring deep research. A key innovation in our framework is the Mind-Map agent, which constructs a structured knowledge graph to store reasoning context and track logical relationships."
-"In the overall process, we deploy a Web</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Cambria Math"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t>‑</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="等线"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Search agent and a Code agent as problem</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Cambria Math"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t>‑</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="等线"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>solving tools, along with a knowledge</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Cambria Math"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t>‑</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="等线"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>graph agent, called Mind</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Cambria Math"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t>‑</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="等线"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Map, to serve as memory."
-" In this paper, we propose AR-MCTS, a universal framework designed to progressively improve the reasoning capabilities of MLLMs through Active Retrieval (AR) and Monte Carlo Tree Search (MCTS). AR-MCTS follows the MCTS algorithm and heuristically integrates an active retrieval mechanism during the expansion stage to automatically acquire high‑quality step‑wise reasoning annotations."
-"We propose AR</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Cambria Math"/>
-        <family val="1"/>
-        <charset val="1"/>
-      </rPr>
-      <t>‑</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="等线"/>
-        <family val="3"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>MCTS, a universal framework dedicated to progressively improving the complex reasoning capabilities of MLLMs through Active Retrieval and Monte Carlo Tree Search."</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve"> "We introduce REAL-MM-RAG, an automatically generated benchmark designed to address four key properties essential for real-world retrieval: (i) multi-modal documents, (ii) enhanced difficulty, (iii) Realistic-RAG queries and (iv) accurate labeling."
-"We identify four essential properties for a real-world document retrieval benchmark, particularly in multi-modal contexts: (i) Multi-modal documents: The dataset should include pages with text, figures, tables, and other visual elements to reflect the complexity of real-world materials. (ii)Enhanced difficulty: Queries should require more than simple keyword matching and involve a large corpus of contextually similar pages to ensure challenging evaluations. (iii) Realistic-RAG queries:Questions must be posed naturally, without explicit references to pages—reflecting queries a person might ask when seeking information without knowing the answer’s location (in contrast to generic question-answering setups). (iv) Accurate labeling: All documents relevant to a query must be correctly and exhaustively labeled to prevent underestimation of retrieval performance and to avoid false negatives"
-"Firstly, each question-answering pair can be categorized by three primary tasks: Understanding, Reasoning, and Locating, as discussed in Section 1. Secondly, we define four types of answer evidences based on element type: (1) Text: pure texts, such as paragraph; (2) Layout: text elements with special layout meaning (generalized text), such as title, header, footer, table name and figure name; (3) Figure: including charts and general images. (4) Table. In addition, each question-answering pair can be classified into single-page or multi-page based on the number of answer evidence pages and single element or cross-element based on the number of types of evidence elements. Based on different primary tasks and answer evidences, we divide our dataset into 20 sub-tasks."</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>REAL-MM-RAG - 2025.acl-long.1528.pdf , 第1页, 第1页；LongDocURL - 2025.acl-long.57.pdf (第4页)</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -1033,31 +763,535 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
+    <t xml:space="preserve"> 什么是SYNQA方法？</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>作者将post-training scaling分为三个主要方法：Supervised Fine-tuning (SFT), Reinforcement Learning (RLxF), and Test-time Compute (TTC).</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SETR模型在训练时具体的训练时间是多少小时？</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>RankCoT 相对于 vanilla RAG 模型的表现如何？这说明了什么？</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>RankCoT 相比 vanilla RAG 模型有 2.5% 的提升，表明它在提供更有意义的细化方面有效，有助于 LLM 更好地回答问题。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <t>"Through empirical evaluation of eight representative LLMs with diverse architectures and scales, we reveal that these noises can be further categorized into two practical groups: noise that is beneficial to LLMs(aka beneficial noise) and noise that is harmful to LLMs (aka harmful noise)."
+" Extensive results show that RAG noises can be categorized into two practical groups: beneficial noise (semantic, datatype, illegal sentence) and harmful noise(counterfactual, supportive, orthographic, prior)."
 “We define seven types of noise and categorize them into two groups: beneficial and harmful noise.”
 “As shown in Figure 2, we categorize RAG noise into seven linguistic types. They are further divided into beneficial (semantic, datatype, and illegal sentence) and harmful noise (counterfactual, supportive, orthographic, and prior) for practical applications.”
 “Based on these trends, we can categorize retrieval noises into two types: harmful noise (counterfactual, supportive, and orthographic) and beneficial noise (semantic, datatype, and illegal sentence).”</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
+    <t>论文 2025.acl-long.250.pdf（NoiserBench），第1页, 第2页,第2页,第3页,第5页</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <t xml:space="preserve">“To bridge this gap, this paper proposes Referencing Evaluation for Long-context Language Models (Ref-Long), a novel benchmark designed to assess the long-context referencing capability of LCLMs.Specifically, Ref-Long requires LCLMs to identify the indexes of documents that reference a specific key, emphasizing contextual relationships between the key and the documents over simple retrieval.”
+"To address the above issues, this work proposes a novel benchmark called Referencing Evaluation for Long-context Language Models (Ref-Long), which is specifically designed to assess the long-context referencing capability of LCLMs. As illustrated in Figure 1, given several indexed long documents and a query that includes “Durant”, LCLMs are required to not only identify “Durant” in the given documents, but also need to figure out the indexes of documents that reference “Durant” rather than other NBA players. First, it considers the relationship information between the specific key and its surrounding context, which forces LCLMs to genuinely understand long contexts instead of simply relying on shortcuts to retrieve the key."
 </t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>论文 2025.acl-long.1162.pdf（Ref-Long），第1页</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve"> 什么是SYNQA方法？</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve"> SYNQA是一种生成合成训练数据的方法，用于训练上下文归因模型。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>作者将post-training scaling分为三个主要方法：Supervised Fine-tuning (SFT), Reinforcement Learning (RLxF), and Test-time Compute (TTC).</t>
+    <t>论文 2025.acl-long.1162.pdf（Ref-Long），第1页, 第2页</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>论文 2025.acl-long.828.pdf，第1页, 第2页, 第3页, 第3页</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>在Humanity's Last Exam数据集上，Agentic Reasoning与DeepSeek-R1结合的性能提升是多少？与OpenAI Deep Research的差距如何变化？</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>α参数的最优范围在0.65到0.8之间。这个参数用于平衡工具描述和参数描述在工具检索中的权重。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve"> 论文 2025.acl-long.1101.pdf(MEMERAG), 第1页, 第3页; 2025.acl-long.418_RAGEval, 第4页, 第5页</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SYNQA 是一种生成式上下文归因数据合成方法。核心思路是：给定选定的上下文句子，由大语言模型（LLM）生成完全受这些句子支持的问题-答案对（QA对）。该方法能够产生反映真实世界多样化问答场景的训练数据，帮助模型学习稳健的归因能力。SYNQA 同时生成以实体为中心和以对话为中心的样本，从而提升模型在不同上下文和领域的泛化能力。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">Agentic Long-Context Understanding (AgenticLU) 是一个旨在增强大语言模型（LLM）对长上下文查询理解能力的框架。其核心是链式澄清（Chain-of-Clarifications, CoC）：模型通过自生成澄清问题、从长上下文中检索相关信息，并基于收集到的证据回答自己的澄清问题，从而动态地精炼推理和理解。
+</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SYNQA 和 RHIO 分别通过什么方式生成训练数据？这两种数据生成策略在提升模型归因能力上有什么不同？</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SYNQA：通过 LLM 生成式合成完全受上下文支持的 QA 对（正样本），用于微调小模型的归因能力。
+RHIO：通过选择性掩码检索头，让 LLM 自身生成模拟真实错误的不忠实样本（负样本），并与忠实样本进行联合训练。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Agentic Reasoning 与 AR-MCTS 分别采用什么核心机制来提升复杂推理能力？</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Agentic Reasoning：动态调用网页搜索、代码执行作为工具，并引入 Mind‑Map 知识图谱智能体作为结构化记忆，存储推理上下文并追踪逻辑关系。
+AR-MCTS：基于蒙特卡洛树搜索（MCTS），在扩展阶段集成主动检索（Active Retrieval） 机制，自动获取逐步推理的高质量标注，渐进式提升多模态大模型的推理能力。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve"> "Agentic Reasoning dynamically leverages web search, code execution, and structured memory to address complex problems requiring deep research. A key innovation in our framework is the Mind-Map agent, which constructs a structured knowledge graph to store reasoning context and track logical relationships."
+"In the overall process, we deploy a Web</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Cambria Math"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t>‑</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Search agent and a Code agent as problem</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Cambria Math"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t>‑</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>solving tools, along with a knowledge</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Cambria Math"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t>‑</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>graph agent, called Mind</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Cambria Math"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t>‑</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Map, to serve as memory."
+"In this paper, we propose AR-MCTS, a universal framework designed to progressively improve the reasoning capabilities of MLLMs through Active Retrieval (AR) and Monte Carlo Tree Search (MCTS). AR-MCTS follows the MCTS algorithm and heuristically integrates an active retrieval mechanism during the expansion stage to automatically acquire high</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Cambria Math"/>
+        <family val="1"/>
+        <charset val="1"/>
+      </rPr>
+      <t>‑</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>quality step</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Cambria Math"/>
+        <family val="1"/>
+        <charset val="1"/>
+      </rPr>
+      <t>‑</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>wise reasoning annotations."
+"We propose AR</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Cambria Math"/>
+        <family val="1"/>
+        <charset val="1"/>
+      </rPr>
+      <t>‑</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>MCTS, a universal framework dedicated to progressively improving the complex reasoning capabilities of MLLMs through Active Retrieval and Monte Carlo Tree Search."</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>实验结果表明，RAGEval 的机器自动评估与人工评估在所有指标上均表现出高度一致性。两者之间的最终绝对差异仅为 1.67%。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve"> REAL-MM-RAG基准测试的四个关键属性是：(i) 多模态文档，(ii) 增强的难度，(iii) 真实的RAG查询，(iv) 准确的标注。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>论文366_How to Train Long-Context Language Models (Effectively),第1页, 第2页, 第8页</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>LongRefiner 在推理时如何降低在线延迟？</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>“Inference. To reduce latency, inference is split into offline and online stages. In the offline stage, the model will perform hierarchical document structuring tasks for the documents in the corpus. In the online stage, it performs an analysis of the user’s query, followed by adaptive refinement to generate the final output. Since the online stage only involves processing hundreds of input tokens and generating dozens of output tokens, the overall latency is only about 25% of the standard setting.”</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2025.acl-long.176_Hierarchical Document Refinement for Long-context Retrieval-augmented Generation ,第6页</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>将推理分为离线阶段和在线阶段。离线阶段完成文档结构化任务，在线阶段仅处理用户查询分析和自适应精炼（输入输出仅数百个 tokens），整体延迟约为标准设置的 25%。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>简述 Think&amp; Cite 框架中 SG-MCTS 的工作流程及其步骤数量。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>在 HALOGEN 的文本简化任务中，如何验证模型生成的简化文本是否忠实于原文？</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>" Decomposition and Verification: We use GPT-3.5 to decompose the model summary with the prompt ‘Please breakdown the following passage into independent facts:’, and Llama-2-70B to provide an entailment decision for each atomic fact."</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2025.acl-long.71_HALoGEN第3页</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>先用 GPT-3.5-turbo 将简化文本分解为独立的原子事实，再用 Llama-2-70B-chat 判断每个原子事实是否被原文蕴含。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve"> "Human physicians surpass Med-MLLMs in diagnostic accuracy across all specialties. Even a junior doctor with an average accuracy of 57.4%, marginally exceeds the most proficient Med-MLLM, GPT-4V, which achieved an accuracy of 54.3%. This outcome suggests that, despite the advancements made in artificial intelligence, there is still a gap in diagnostic precision between human expertise and current Med-MLLMs."
+"Comparing the Med</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Cambria Math"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t>‑</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>MLLMs to human doctors, all the Med</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Cambria Math"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t>‑</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>MLLMs have a lower average accuracy than the human doctors. Among the Med</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Cambria Math"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t>‑</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>MLLMs, GPT</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Cambria Math"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t>‑</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>4V's performance is closest to that of human doctors, which surpasses Doctor2 by a small margin with an accuracy of 0.005.”</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2025.acl-long.1178.pdf (第7页, 第14页)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>REAL-MM-RAG 基准测试旨在解决现实世界检索的四个关键属性是什么？</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>RAGEval 提出的自动评估指标与人工评估的一致性如何？</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>“for SFT, using only short instruction datasets yields strong performance on long-context tasks.”
+"We find that SFT with standard, short-context instruction datasets is sufficient for achieving good performance.Contrary to previous study, long synthetic instruction data does not further boost the performance."
+"however, we find that using standard,short-context instruction data achieves the best long-context results in our setting."</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>MAIN</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Cambria Math"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t>‑</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>RAG 与 RAG</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Cambria Math"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t>‑</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Critic 在提升 RAG 系统可靠性方面分别采用了什么核心方法？</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>MAIN</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Cambria Math"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t>‑</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>RAG 采用多智能体协作过滤机制，通过三个 LLM 智能体（Predictor、Judge、Final</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Cambria Math"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t>‑</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Predictor）对检索文档进行相关性评分和排序，并利用自适应阈值动态过滤噪声文档，无需训练。
+RAG</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Cambria Math"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t>‑</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Critic 采用批评引导的智能体工作流，首先构建层次化 RAG 错误系统（3 级错误类型，含 4000+ 细粒度标签），然后训练轻量级错误批评模型进行自动错误诊断，最后通过规划智能体根据错误反馈定制并执行修正方案。</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>“To address these challenges, we propose MultiAgent Filtering Retrieval-Augmented Generation (MAIN-RAG), a novel training-free framework designed to enhance the performance and reliability of RAG systems. Unlike existing methods that often rely on computationally intensive training or fine-tuning, MAIN-RAG leverages a collaborative multi-agent approach where multiple LLM agents filter and score retrieved documents. This consensus-driven strategy ensures that only the most relevant and high-quality documents are utilized for generation, significantly reducing noise without sacrificing recall.”
+“The proposed framework MAIN-RAG is to identify noisy retrieved documents for filtering out, consisting of three LLM agents: Agent-1 (Predictor), Agent-2 (Judge), and Agent-3 (Final-Predictor).”
+“We propose RAG-Critic, a novel framework that leverages a critic-guided agentic workflow to improve RAG capabilities autonomously. Specifically, we initially design a data-driven error mining pipeline to establish a hierarchical RAG error system. Based on this system, we progressively align an error-critic model using a coarse-to-fine training objective, which automatically provides fine-grained error feedback. Finally, we design a critic-guided agentic RAG workflow that customizes executor-based solution flows based on the error-critic model’s feedback, facilitating an error-driven self-correction process.”
+"In this paper, we introduce RAG-Critic, a novel framework that utilizes a critic-guided agentic workflow to autonomously enhance RAG capabilities. We first design a data-driven error mining pipeline to establish a hierarchical RAG error system. Using this system, we progressively align an error-critic model with a coarse-to-fine training objective, automating the fine-grained error feedback. We then introduce the critic-guided agentic workflow, which facilitates an error-driven correction by autonomously customizing executor-based solution flows based on error feedback."</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2025.acl-long.131_MAIN-RAG.pdf 第1页, 第3页
+2025.acl-long.179_RAG-Critic.pdf 第1页, 第9页</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>"Results in Figure 7 show that the machine and human evaluations show a high degree of alignment in all metrics. The final absolute difference between the human evaluation and the machine evaluation is 1.67%."
+"Furthermore, the use of LLMs for scoring the proposed metrics demonstrates a high level of consistency with human evaluations."</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2025.acl-long.418_RAGEval.pdf, 第11页, 第1页</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>RAG噪声被分为有益噪声和有害噪声。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>在SafeRAG中"silver noise"的定义是什么？</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1446,175 +1680,175 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="2" spans="1:4" ht="168" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
-        <v>116</v>
+        <v>87</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>182</v>
+        <v>139</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>118</v>
+        <v>89</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>121</v>
+        <v>92</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="98" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
-        <v>81</v>
+        <v>182</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>117</v>
+        <v>88</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>119</v>
+        <v>90</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" ht="238" x14ac:dyDescent="0.3">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" ht="308" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
-        <v>80</v>
+        <v>63</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>79</v>
+        <v>181</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>177</v>
+        <v>143</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" ht="140" x14ac:dyDescent="0.3">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" ht="350" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>123</v>
+        <v>93</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>178</v>
+        <v>145</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>179</v>
+        <v>146</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="280" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
-        <v>180</v>
+        <v>138</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>181</v>
+        <v>151</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>124</v>
+        <v>94</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>125</v>
+        <v>147</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="364" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>26</v>
+        <v>152</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>126</v>
+        <v>95</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>127</v>
+        <v>96</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="84" x14ac:dyDescent="0.3">
       <c r="A8" s="3" t="s">
-        <v>87</v>
+        <v>69</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>128</v>
+        <v>97</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>129</v>
+        <v>98</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="378" x14ac:dyDescent="0.3">
       <c r="A9" s="3" t="s">
-        <v>42</v>
+        <v>172</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>43</v>
+        <v>159</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>130</v>
+        <v>99</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>131</v>
+        <v>100</v>
       </c>
     </row>
     <row r="10" spans="1:4" ht="210" x14ac:dyDescent="0.3">
       <c r="A10" s="3" t="s">
-        <v>89</v>
+        <v>71</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>88</v>
+        <v>70</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>132</v>
+        <v>101</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>133</v>
+        <v>102</v>
       </c>
     </row>
     <row r="11" spans="1:4" ht="224" x14ac:dyDescent="0.3">
       <c r="A11" s="3" t="s">
-        <v>66</v>
+        <v>52</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>67</v>
+        <v>53</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>134</v>
+        <v>103</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>68</v>
+        <v>54</v>
       </c>
     </row>
     <row r="12" spans="1:4" ht="126" x14ac:dyDescent="0.3">
       <c r="A12" s="1" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>135</v>
+        <v>104</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>136</v>
+        <v>105</v>
       </c>
     </row>
     <row r="13" spans="1:4" ht="409.5" x14ac:dyDescent="0.3">
       <c r="A13" s="1" t="s">
-        <v>111</v>
+        <v>85</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>137</v>
+        <v>106</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>138</v>
+        <v>107</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>139</v>
+        <v>108</v>
       </c>
     </row>
   </sheetData>
@@ -1646,21 +1880,21 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" ht="126" x14ac:dyDescent="0.3">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" ht="168" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
-        <v>56</v>
+        <v>44</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>57</v>
+        <v>45</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>140</v>
+        <v>174</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>141</v>
+        <v>160</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="182" x14ac:dyDescent="0.3">
@@ -1668,139 +1902,139 @@
         <v>3</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>84</v>
+        <v>66</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>142</v>
+        <v>109</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" ht="112" x14ac:dyDescent="0.3">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" ht="168" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
-        <v>112</v>
+        <v>161</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>7</v>
+        <v>164</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>144</v>
+        <v>162</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>55</v>
+        <v>163</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="392" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>59</v>
+        <v>47</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>145</v>
+        <v>111</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>146</v>
+        <v>112</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="98" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
-        <v>91</v>
+        <v>165</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>90</v>
+        <v>72</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>147</v>
+        <v>113</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>148</v>
+        <v>114</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="154" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
-        <v>92</v>
+        <v>73</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>93</v>
+        <v>74</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>94</v>
+        <v>75</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>95</v>
+        <v>76</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="126" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>34</v>
+        <v>149</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" ht="70" x14ac:dyDescent="0.3">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" ht="112" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
-        <v>113</v>
+        <v>77</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>114</v>
+        <v>78</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>60</v>
+        <v>115</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" ht="112" x14ac:dyDescent="0.3">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" ht="210" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
-        <v>96</v>
+        <v>38</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>97</v>
+        <v>39</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>149</v>
+        <v>40</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" ht="210" x14ac:dyDescent="0.3">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" ht="154" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="s">
-        <v>47</v>
+        <v>117</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>48</v>
+        <v>118</v>
       </c>
       <c r="C11" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="D11" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="D11" s="1" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" ht="154" x14ac:dyDescent="0.3">
+    </row>
+    <row r="12" spans="1:4" ht="84" x14ac:dyDescent="0.3">
       <c r="A12" s="1" t="s">
-        <v>151</v>
+        <v>166</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>152</v>
+        <v>169</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>82</v>
+        <v>167</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>63</v>
+        <v>168</v>
       </c>
     </row>
   </sheetData>
@@ -1830,7 +2064,7 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="2" spans="1:4" ht="70" x14ac:dyDescent="0.3">
@@ -1844,147 +2078,147 @@
         <v>6</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>153</v>
+        <v>119</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="56" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="C3" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C3" s="1" t="s">
-        <v>11</v>
-      </c>
       <c r="D3" s="1" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" ht="84" x14ac:dyDescent="0.3">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" ht="70" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
-        <v>98</v>
+        <v>141</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>154</v>
+        <v>142</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>65</v>
+        <v>51</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>64</v>
+        <v>50</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="70" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
-        <v>103</v>
+        <v>79</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>104</v>
+        <v>80</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>69</v>
+        <v>55</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="126" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>155</v>
+        <v>120</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>156</v>
+        <v>121</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="140" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
-        <v>158</v>
+        <v>123</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>159</v>
+        <v>124</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>157</v>
+        <v>122</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>70</v>
+        <v>56</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="70" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
-        <v>38</v>
+        <v>148</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="112" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>72</v>
+        <v>58</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>160</v>
+        <v>125</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" ht="140" x14ac:dyDescent="0.3">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" ht="409.5" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>46</v>
+        <v>170</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>73</v>
+        <v>171</v>
       </c>
     </row>
     <row r="11" spans="1:4" ht="168" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="s">
-        <v>74</v>
+        <v>59</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>52</v>
+        <v>41</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>83</v>
+        <v>65</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" ht="98" x14ac:dyDescent="0.3">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" ht="112" x14ac:dyDescent="0.3">
       <c r="A12" s="1" t="s">
-        <v>100</v>
+        <v>173</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>99</v>
+        <v>158</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>101</v>
+        <v>179</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>102</v>
+        <v>180</v>
       </c>
     </row>
   </sheetData>
@@ -2014,119 +2248,119 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="2" spans="1:4" ht="266" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
-        <v>105</v>
+        <v>81</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>161</v>
+        <v>126</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>162</v>
+        <v>127</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>163</v>
+        <v>128</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="409.5" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>164</v>
+        <v>129</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>165</v>
+        <v>130</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>166</v>
+        <v>131</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="196" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>76</v>
+        <v>61</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>168</v>
+        <v>132</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>167</v>
+        <v>150</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="196" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
-        <v>23</v>
+        <v>153</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>106</v>
+        <v>154</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>169</v>
+        <v>133</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>170</v>
+        <v>134</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="154" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
-        <v>107</v>
+        <v>82</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>110</v>
+        <v>84</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>77</v>
+        <v>62</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="409.5" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
-        <v>50</v>
+        <v>155</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>78</v>
+        <v>156</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>172</v>
+        <v>157</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>171</v>
+        <v>135</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="409.5" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
-        <v>108</v>
+        <v>175</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>51</v>
+        <v>176</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>174</v>
+        <v>178</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="365.5" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
-        <v>115</v>
+        <v>86</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>109</v>
+        <v>83</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>175</v>
+        <v>136</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>176</v>
+        <v>137</v>
       </c>
     </row>
   </sheetData>
@@ -2155,119 +2389,119 @@
         <v>2</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="2" spans="1:4" ht="28" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>86</v>
+        <v>68</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="28" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>86</v>
+        <v>68</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" ht="28" x14ac:dyDescent="0.3">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
-        <v>16</v>
+        <v>140</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>86</v>
+        <v>68</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="42" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>86</v>
+        <v>68</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="28" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>86</v>
+        <v>68</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="28" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>86</v>
+        <v>68</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="28" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
-        <v>53</v>
+        <v>42</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>86</v>
+        <v>68</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="28" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
-        <v>54</v>
+        <v>43</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>86</v>
+        <v>68</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
   </sheetData>

--- a/code/测试集.xlsx
+++ b/code/测试集.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\rag_project\code\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A32E49B-9175-4E45-981A-4465514C711F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{926AFFCC-1877-4B84-A7BB-EAD412D37C35}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="12710" yWindow="0" windowWidth="12980" windowHeight="13770" firstSheet="1" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="定义类" sheetId="1" r:id="rId1"/>
@@ -122,10 +122,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>"We find that all LLMs make a considerable number of factual errors, with even the best-performing LLMs hallucinating between 3%-86% of the facts generated, depending on the domain."</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>论文中是否提到了SYNQA方法在医疗领域的具体应用案例？</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -219,14 +215,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>在论文《How to Train Long-Context Language Models (Effectively)》中，作者在进行监督微调（SFT）阶段时，对于长上下文模型的指令微调数据选择得出了什么反直觉的结论？</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>作者发现，仅使用标准的、短上下文的指令数据集（如 UltraChat）进行微调，就能在长上下文任务上取得最佳效果。反直觉的是，引入合成的长上下文指令数据（synthetic long instruction data）并没有提升性能，甚至在某些比例下导致了性能下降。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>2025.acl-long.1062_FaithfulRAG ,第7页</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -239,18 +227,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>2025.acl-long.217.pdf (第1页)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>论文 2025.acl-long.629.pdf（RankCoT），第6页</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>"In contrast, RankCoT demonstrates a 2.5% improvement over vanilla RAG model, indicating its effectiveness in providing more meaningful refinements that help LLMs better answer questions."</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>L-CiteEval的定义是什么？</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -259,14 +235,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>2025.acl-long.263_L-CiteEval.pdf, 第一页</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve"> 论文 2025.acl-long.71.pdf，第5页</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>论文 2025.acl-long.1355.pdf，第7页</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -280,10 +248,6 @@
   </si>
   <si>
     <t>在LongDocURL基准测试中，GPT-4o的表现如何？其他开源模型呢？</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve"> 2025.acl-long.57.pdf (第6页)</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -297,14 +261,6 @@
   </si>
   <si>
     <t>RAG噪声被分为哪两类？</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>"We introduce QAEncoder, a training-free approach to bridge this gap. Specifically, QAEncoder estimates the expectation of potential queries in the embedding space as a robust surrogate for the document embedding, and attaches document fingerprints to effectively distinguish these embeddings. ."</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>"Only GPT-4o meets the passing standard and scores highest at 64.5, indicating that our LongDocURL presents significant challenges for current models. (2) Comparison of Open-source and Closed-source models: Proprietary models demonstrate better overall performance compared to open source models. Among open-source models, only Qwen2-VL (score 30.6) and LLaVA-OneVision(scores 22.0 and 25.0) exceed a score of 20, while other models with fewer than 13B parameters fall below this threshold."</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -354,10 +310,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>论文 2025.acl-long.861.pdf（SETR），第3页</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>CypherBench 是如何从 RDF 图生成领域特定属性图的？</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -465,21 +417,6 @@
   </si>
   <si>
     <t>2025.acl-long.1528.pdf , 第一页, 第一页</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>"To render LLMs resilient to imperfect retrieval, we propose ASTUTE RAG, a novel RAG approach that adaptively elicits essential information from LLMs' internal knowledge, iteratively consolidates internal and external knowledge with source-awareness, and finalizes the answer according to information reliability."
-“We propose ASTUTE RAG, which explicitly analyzes LLM-internal and external knowledge in-context, assesses their reliability, and recovers from RAG failures with black-box access.”
-“ASTUTE RAG is designed to better leverage collective knowledge from both internal knowledge of LLMs and external corpus, for more reliable responses.”</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>2025.acl-long.1476_Astute RAG.pdf, 第1页, 第二页, 第五页</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>“We introduce L-CiteEval, an out-of-the-box suite that can assess both generation quality and fidelity in long-context understanding tasks. It covers 11 tasks with context lengths ranging from 8K to 48K and a corresponding automatic evaluation pipeline.”
-"To mitigate the above issues in long-context evaluation field, we propose an out-of-the-box evaluation suite, L-CiteEval, which requires LCMs to generate both the statements and their supporting evidence (citations). This suite comprises two key components: (1) a comprehensive benchmark encompassing 5 major task categories and 11 diverse long-context tasks, with context lengths ranging from 8K to 48K; and (2) corresponding automatic evaluation metrics and verification pipelines to ensure robust and reliable assessment."</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -515,10 +452,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>2025.acl-long.1476_Astute RAG, 第2页,第5页</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>“Another key advantage of our framework is its potential for privacy protection. Typically, when querying large- scale LLMs, local deployment is not feasible, requiring users to upload their private queries to cloud- based LLMs, raising privacy concerns. Our framework addresses this issue by enabling local SLMs to leverage the knowledge of large models while preserving user privacy."
 "With our approach, the local model first reformulates the query (much simpler than answering the query directly), stripping any sensitive information before sending it to the cloud- based model. The cloud model then retrieves relevant evidence and knowledge graphs, which are subsequently passed back to the local model for final processing and response generation. This ensures that private data remains protected while still benefiting from the power of large- scale LLMs.”
 “2) The teacher LLM is usually heavy in size and deployed on the cloud, and the student is on local devices, it is simple to develop methods for preserving privacy using our proposed framework by transmitting only de- identified queries and structured knowledge instead of full responses, as we have introduced in Section 3.3.”</t>
@@ -557,19 +490,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>2025.acl-long.1574_CiteEval , 第8页</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>"We employ both automated and manual review processes to maintain high quality and difficulty, resulting in human experts achieving only 53.7% accuracy under a 15-minute time constraint."
-"Human experts are able to achieve an accuracy of 53.7% within 15 minutes, compared to 25% accuracy with random guessing, highlighting the challenging nature of the test."</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve"> 论文 2025.acl-long.183.pdf，第1页, 第2页</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>"For instance, agents with AGENTSTAR outperform GPT-4-Turbo and AGENTTRAJ-L-SFT by 61.00 and 3.00 points on WebShop (Yao et al., 2022), 20.50 and 5.00 points on ALFWorld (Shridhar et al., 2021), and 9.87 and 8.51 points on BabyAI (Chevalier-Boisvert et al., 2019). This validates the superiority and promise of the exploration and learning paradigm in developing agents (Zelikman et al., 2022)."</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -591,118 +511,7 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>"FaithfulRAG adopts a novel self-fact mining module to externalize the LLM’s understanding of the question, obtaining fine-grained knowledge at the fact level."
-"Our approach addresses both aspects by employing a hierarchical,three-stage process that externalizes the model’s internal knowledge into distinct logical and fine-grained factual representations.Specifically, for a given question Q, our objective is to extract the essential factual and conceptual information required to answer Q while filtering out unnecessary details. We achieve this through the following three sequential stages: Self Knowledge Extraction,Self-Context Generation and Self-Fact Extraction."
-"To achieve this goal, we enhance the original method with constitutional principles and adaptive generatio.n"
-"Moreover, we allow the LLM to perform adaptive generation of passages in its internal knowledge. The LLM can decide how many passages to generate by itself."</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>《FaithfulRAG》,第2页
-《FaithfulRAG》,第4页
-《Astute RAG》, 第5页
-《Astute RAG》, 第5页</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>UniRAG提出统一的查询理解框架，集成查询增强和查询编码两个阶段；FaithfulRAG通过自我事实挖掘和自思考模块，在事实级别识别并解决参数化知识与检索上下文之间的冲突，提高语义一致性。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>"In this work, we propose UniRAG, a unified framework for query understanding in RAG. UniRAG employs a decoder only LLM to jointly perform query augmentation and encoding, eliminating task separation."
-"To address these challenges, this work introduces UniRAG. As shown on the right side of Figure 1, we achieve unified execution of query augmentation and query encoding by training a decoder</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Cambria Math"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t>‑</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="等线"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>only LLM."
-"FaithfulRAG identifies conflicting knowledge at the fact level and designs a self</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Cambria Math"/>
-        <family val="1"/>
-        <charset val="1"/>
-      </rPr>
-      <t>‑</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="等线"/>
-        <family val="3"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>thinking process, allowing LLMs to reason about and integrate conflicting facts before generating responses."
-"FaithfulRAG adopts a novel self</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Cambria Math"/>
-        <family val="1"/>
-        <charset val="1"/>
-      </rPr>
-      <t>‑</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="等线"/>
-        <family val="3"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>fact mining module to externalize the LLM's understanding of the question, obtaining fine</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Cambria Math"/>
-        <family val="1"/>
-        <charset val="1"/>
-      </rPr>
-      <t>‑</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="等线"/>
-        <family val="3"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>grained knowledge at the fact level."
-"FaithfulRAG first designs a self-fact mining module to externalize the LLM’s understanding of the question, obtaining fine-grained knowledge at the fact level. Then itidentifies conflicting knowledge by aligning self-fact with the retrieved contexts and adopts a self-thinking module,allowing LLMs to reason about and integrate conflicting facts before generating responses."</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>2025.acl-long.693_UniRAG , 第1页, 第1页 ;  2025.acl-long.1062_FaithfulRAG , 第1页, 第2页, 第4页</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -722,44 +531,6 @@
   <si>
     <t>SYNQA: 2025.acl-long.828.pdf，第1页, 第1页
 RHIO: 2025.acl-long.826.pdf，第1页, 第3页</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Agentic Reasoning - 2025.acl-long.1383.pdf , 第1页, 第2页；AR-MCTS - 2025.acl-long.180.pdf , 第1页, 第2页</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>“However, the inherent gap between user queries and relevant documents hinders precise matching. We introduce QAEncoder, a training</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Cambria Math"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t>‑</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="等线"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">free approach to bridge this gap.”
-"Despite advancements, a significant challenge that persists is bridging the gap between user queries and documents across lexical, syntactic, semantic, and content dimensions(Zheng et al., 2020;Nogueira et al., 2019; Cheriton, 2019),termed the document-query gap."
-“However, LLMs sometimes produce false or misleading responses, also known as hallucinations. Therefore, grounding the generated answers in contextually provided information i.e., providing evidence for the generated text is paramount for LLMs' trustworthiness. Providing this information is the task of context attribution.”
-“This poses the need for context attribution methods that create links between the answer and different relevant parts of the (potentially large) reference text.”
-</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>2025.acl-long.217_QAEncoder.pdf, 第1页, 第1页; 2025.acl-long.828_On Synthesizing Data for Context Attribution in Question Answering, 第1页, 第1页</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -848,9 +619,58 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <r>
-      <t xml:space="preserve"> "Agentic Reasoning dynamically leverages web search, code execution, and structured memory to address complex problems requiring deep research. A key innovation in our framework is the Mind-Map agent, which constructs a structured knowledge graph to store reasoning context and track logical relationships."
-"In the overall process, we deploy a Web</t>
+    <t>实验结果表明，RAGEval 的机器自动评估与人工评估在所有指标上均表现出高度一致性。两者之间的最终绝对差异仅为 1.67%。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve"> REAL-MM-RAG基准测试的四个关键属性是：(i) 多模态文档，(ii) 增强的难度，(iii) 真实的RAG查询，(iv) 准确的标注。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>论文366_How to Train Long-Context Language Models (Effectively),第1页, 第2页, 第8页</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>LongRefiner 在推理时如何降低在线延迟？</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>将推理分为离线阶段和在线阶段。离线阶段完成文档结构化任务，在线阶段仅处理用户查询分析和自适应精炼（输入输出仅数百个 tokens），整体延迟约为标准设置的 25%。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>在 HALOGEN 的文本简化任务中，如何验证模型生成的简化文本是否忠实于原文？</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>" Decomposition and Verification: We use GPT-3.5 to decompose the model summary with the prompt ‘Please breakdown the following passage into independent facts:’, and Llama-2-70B to provide an entailment decision for each atomic fact."</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2025.acl-long.71_HALoGEN第3页</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>先用 GPT-3.5-turbo 将简化文本分解为独立的原子事实，再用 Llama-2-70B-chat 判断每个原子事实是否被原文蕴含。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>REAL-MM-RAG 基准测试旨在解决现实世界检索的四个关键属性是什么？</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>RAGEval 提出的自动评估指标与人工评估的一致性如何？</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>“for SFT, using only short instruction datasets yields strong performance on long-context tasks.”
+"We find that SFT with standard, short-context instruction datasets is sufficient for achieving good performance.Contrary to previous study, long synthetic instruction data does not further boost the performance."
+"however, we find that using standard,short-context instruction data achieves the best long-context results in our setting."</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>MAIN</t>
     </r>
     <r>
       <rPr>
@@ -870,7 +690,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>Search agent and a Code agent as problem</t>
+      <t>RAG 与 RAG</t>
     </r>
     <r>
       <rPr>
@@ -890,7 +710,13 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>solving tools, along with a knowledge</t>
+      <t>Critic 在提升 RAG 系统可靠性方面分别采用了什么核心方法？</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>MAIN</t>
     </r>
     <r>
       <rPr>
@@ -910,7 +736,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>graph agent, called Mind</t>
+      <t>RAG 采用多智能体协作过滤机制，通过三个 LLM 智能体（Predictor、Judge、Final</t>
     </r>
     <r>
       <rPr>
@@ -930,8 +756,140 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>Map, to serve as memory."
-"In this paper, we propose AR-MCTS, a universal framework designed to progressively improve the reasoning capabilities of MLLMs through Active Retrieval (AR) and Monte Carlo Tree Search (MCTS). AR-MCTS follows the MCTS algorithm and heuristically integrates an active retrieval mechanism during the expansion stage to automatically acquire high</t>
+      <t>Predictor）对检索文档进行相关性评分和排序，并利用自适应阈值动态过滤噪声文档，无需训练。
+RAG</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Cambria Math"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t>‑</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Critic 采用批评引导的智能体工作流，首先构建层次化 RAG 错误系统（3 级错误类型，含 4000+ 细粒度标签），然后训练轻量级错误批评模型进行自动错误诊断，最后通过规划智能体根据错误反馈定制并执行修正方案。</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>“To address these challenges, we propose MultiAgent Filtering Retrieval-Augmented Generation (MAIN-RAG), a novel training-free framework designed to enhance the performance and reliability of RAG systems. Unlike existing methods that often rely on computationally intensive training or fine-tuning, MAIN-RAG leverages a collaborative multi-agent approach where multiple LLM agents filter and score retrieved documents. This consensus-driven strategy ensures that only the most relevant and high-quality documents are utilized for generation, significantly reducing noise without sacrificing recall.”
+“The proposed framework MAIN-RAG is to identify noisy retrieved documents for filtering out, consisting of three LLM agents: Agent-1 (Predictor), Agent-2 (Judge), and Agent-3 (Final-Predictor).”
+“We propose RAG-Critic, a novel framework that leverages a critic-guided agentic workflow to improve RAG capabilities autonomously. Specifically, we initially design a data-driven error mining pipeline to establish a hierarchical RAG error system. Based on this system, we progressively align an error-critic model using a coarse-to-fine training objective, which automatically provides fine-grained error feedback. Finally, we design a critic-guided agentic RAG workflow that customizes executor-based solution flows based on the error-critic model’s feedback, facilitating an error-driven self-correction process.”
+"In this paper, we introduce RAG-Critic, a novel framework that utilizes a critic-guided agentic workflow to autonomously enhance RAG capabilities. We first design a data-driven error mining pipeline to establish a hierarchical RAG error system. Using this system, we progressively align an error-critic model with a coarse-to-fine training objective, automating the fine-grained error feedback. We then introduce the critic-guided agentic workflow, which facilitates an error-driven correction by autonomously customizing executor-based solution flows based on error feedback."</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2025.acl-long.131_MAIN-RAG.pdf 第1页, 第3页
+2025.acl-long.179_RAG-Critic.pdf 第1页, 第9页</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>"Results in Figure 7 show that the machine and human evaluations show a high degree of alignment in all metrics. The final absolute difference between the human evaluation and the machine evaluation is 1.67%."
+"Furthermore, the use of LLMs for scoring the proposed metrics demonstrates a high level of consistency with human evaluations."</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2025.acl-long.418_RAGEval.pdf, 第11页, 第1页</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>RAG噪声被分为有益噪声和有害噪声。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>在SafeRAG中"silver noise"的定义是什么？</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>简述 Think&amp; Cite 框架中 SG-MCTS 的工作流程及其步骤。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>在How to Train Long-Context Language Models中的监督微调（SFT）阶段，论文作者发现使用哪种类型的数据集能够在长上下文任务上取得最佳性能？</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>作者发现，仅使用标准的、短上下文的指令数据集（如 UltraChat）进行微调，就能在长上下文任务上取得最佳效果。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2025.acl-long.1574_CiteEval , 第8页, 表格在第7页</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>"We find that all LLMs make a considerable number of factual errors, with even the best-performing LLMs hallucinating between 3%-86% of the facts generated, depending on the domain."
+"Our experimental results show that even the best performing LLM responses are riddled with hallucination errors, with hallucination scores ranging from 3% to 86% depending on the task for GPT-4."</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve"> 论文 2025.acl-long.71.pdf，第5页,第1页</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>"Only GPT-4o meets the passing standard and scores highest at 64.5, indicating that our LongDocURL presents significant challenges for current models. (2) Comparison of Open-source and Closed-source models: Proprietary models demonstrate better overall performance compared to open source models. Among open-source models, only Qwen2-VL (score 30.6) and LLaVA-OneVision(scores 22.0 and 25.0) exceed a score of 20, while other models with fewer than 13B parameters fall below this threshold."
+"These evaluation results indicate that the highest-performing closed-source model, GPT-4o, scored 64.5, leading all models, while the best score for open-source models is only 30.6. This result reveals a potential gap in document understanding and shows the need for further improvement. "</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve"> 2025.acl-long.57.pdf (第6页), 第2页</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2025.acl-long.263_L-CiteEval.pdf, 第一页, 第1页, 第8页</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>“We introduce L-CiteEval, an out-of-the-box suite that can assess both generation quality and fidelity in long-context understanding tasks. It covers 11 tasks with context lengths ranging from 8K to 48K and a corresponding automatic evaluation pipeline.”
+"To mitigate the above issues in long-context evaluation field, we propose an out-of-the-box evaluation suite, L-CiteEval, which requires LCMs to generate both the statements and their supporting evidence (citations). This suite comprises two key components: (1) a comprehensive benchmark encompassing 5 major task categories and 11 diverse long-context tasks, with context lengths ranging from 8K to 48K; and (2) corresponding automatic evaluation metrics and verification pipelines to ensure robust and reliable assessment."
+"Inthispaper,weintroduceL-CiteEval,anout-of the-boxevaluationsuitefeaturingamulti-tasklong contextbenchmarkandacorrespondingevaluation pipeline. Thebenchmarkincludes5major task categoriesspanning11long-context tasks,with context lengths rangingfrom8Kto48K.Com prehensivetestingacross11state-of-the-artLCMs revealsthatopen-sourceLCMsoftenrelyonintrin sicknowledgeratherthantheprovidedcontextto generateresponses."</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve"> 论文 2025.acl-long.183.pdf，第1页, 第2页, 第7页</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>"We employ both automated and manual review processes to maintain high quality and difficulty, resulting in human experts achieving only 53.7% accuracy under a 15-minute time constraint."
+"Human experts are able to achieve an accuracy of 53.7% within 15 minutes, compared to 25% accuracy with random guessing, highlighting the challenging nature of the test."
+"Thebest-performingo1-preview model achievesonly57.7%accuracy,which is 4%higherthantheperformanceofhumanexperts undera15-minutetimelimit."</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>"In this work, we propose UniRAG, a unified framework for query understanding in RAG. UniRAG employs a decoder only LLM to jointly perform query augmentation and encoding, eliminating task separation."
+"In this work, we propose UniRAG, a unified query understanding framework for retrieval-augmented generation. By integrating query augmentation and encoding within a single model, UniRAG improves information sharing and reduces cumulative errors.Through adaptive selection of augmentation strategies and contrastive learning, our approach signif icantly boosts retrieval performance. "
+"To address these challenges, this work introduces UniRAG. As shown on the right side of Figure 1, we achieve unified execution of query augmentation and query encoding by training a decoder</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Cambria Math"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t>‑</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>only LLM."
+"FaithfulRAG identifies conflicting knowledge at the fact level and designs a self</t>
     </r>
     <r>
       <rPr>
@@ -952,7 +910,8 @@
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
-      <t>quality step</t>
+      <t>thinking process, allowing LLMs to reason about and integrate conflicting facts before generating responses."
+"FaithfulRAG adopts a novel self</t>
     </r>
     <r>
       <rPr>
@@ -973,8 +932,7 @@
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
-      <t>wise reasoning annotations."
-"We propose AR</t>
+      <t>fact mining module to externalize the LLM's understanding of the question, obtaining fine</t>
     </r>
     <r>
       <rPr>
@@ -995,56 +953,33 @@
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
-      <t>MCTS, a universal framework dedicated to progressively improving the complex reasoning capabilities of MLLMs through Active Retrieval and Monte Carlo Tree Search."</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>实验结果表明，RAGEval 的机器自动评估与人工评估在所有指标上均表现出高度一致性。两者之间的最终绝对差异仅为 1.67%。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve"> REAL-MM-RAG基准测试的四个关键属性是：(i) 多模态文档，(ii) 增强的难度，(iii) 真实的RAG查询，(iv) 准确的标注。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>论文366_How to Train Long-Context Language Models (Effectively),第1页, 第2页, 第8页</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>LongRefiner 在推理时如何降低在线延迟？</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>“Inference. To reduce latency, inference is split into offline and online stages. In the offline stage, the model will perform hierarchical document structuring tasks for the documents in the corpus. In the online stage, it performs an analysis of the user’s query, followed by adaptive refinement to generate the final output. Since the online stage only involves processing hundreds of input tokens and generating dozens of output tokens, the overall latency is only about 25% of the standard setting.”</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>2025.acl-long.176_Hierarchical Document Refinement for Long-context Retrieval-augmented Generation ,第6页</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>将推理分为离线阶段和在线阶段。离线阶段完成文档结构化任务，在线阶段仅处理用户查询分析和自适应精炼（输入输出仅数百个 tokens），整体延迟约为标准设置的 25%。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>简述 Think&amp; Cite 框架中 SG-MCTS 的工作流程及其步骤数量。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>在 HALOGEN 的文本简化任务中，如何验证模型生成的简化文本是否忠实于原文？</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>" Decomposition and Verification: We use GPT-3.5 to decompose the model summary with the prompt ‘Please breakdown the following passage into independent facts:’, and Llama-2-70B to provide an entailment decision for each atomic fact."</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>2025.acl-long.71_HALoGEN第3页</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>先用 GPT-3.5-turbo 将简化文本分解为独立的原子事实，再用 Llama-2-70B-chat 判断每个原子事实是否被原文蕴含。</t>
+      <t>grained knowledge at the fact level."
+"FaithfulRAG first designs a self-fact mining module to externalize the LLM’s understanding of the question, obtaining fine-grained knowledge at the fact level. Then itidentifies conflicting knowledge by aligning self-fact with the retrieved contexts and adopts a self-thinking module,allowing LLMs to reason about and integrate conflicting facts before generating responses."</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+“To address these challenges, we propose a novel faithful framework (FaithfulRAG) that explicitly identifies and resolves knowledge conflicts at the fact level.”</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2025.acl-long.693_UniRAG , 第1页, 第1页, 第9页 ;  2025.acl-long.1062_FaithfulRAG , 第1页, 第2页, 第4页, 第9页</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>“Inference. To reduce latency, inference is split into offline and online stages. In the offline stage, the model will perform hierarchical document structuring tasks for the documents in the corpus. In the online stage, it performs an analysis of the user’s query, followed by adaptive refinement to generate the final output. Since the online stage only involves processing hundreds of input tokens and generating dozens of output tokens, the overall latency is only about 25% of the standard setting.”
+“We developed an efficient inference paradigm that achieves low online latency by executing certain tasks offline.”</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2025.acl-long.176_Hierarchical Document Refinement for Long-context Retrieval-augmented Generation ,第6页, 第2页</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -1130,31 +1065,15 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>4V's performance is closest to that of human doctors, which surpasses Doctor2 by a small margin with an accuracy of 0.005.”</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>2025.acl-long.1178.pdf (第7页, 第14页)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>REAL-MM-RAG 基准测试旨在解决现实世界检索的四个关键属性是什么？</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>RAGEval 提出的自动评估指标与人工评估的一致性如何？</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>“for SFT, using only short instruction datasets yields strong performance on long-context tasks.”
-"We find that SFT with standard, short-context instruction datasets is sufficient for achieving good performance.Contrary to previous study, long synthetic instruction data does not further boost the performance."
-"however, we find that using standard,short-context instruction data achieves the best long-context results in our setting."</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>MAIN</t>
+      <t>4V's performance is closest to that of human doctors, which surpasses Doctor2 by a small margin with an accuracy of 0.005.”
+"Our analysis reveals a broad spectrum of accuracy scores across the medical specialties in Figure 5. GPT-4V generally has the highest performance among the Med-MLLMs, with its average accuracy closest to human doctors."</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve"> "Agentic Reasoning dynamically leverages web search, code execution, and structured memory to address complex problems requiring deep research. A key innovation in our framework is the Mind-Map agent, which constructs a structured knowledge graph to store reasoning context and track logical relationships."
+"In the overall process, we deploy a Web</t>
     </r>
     <r>
       <rPr>
@@ -1174,7 +1093,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>RAG 与 RAG</t>
+      <t>Search agent and a Code agent as problem</t>
     </r>
     <r>
       <rPr>
@@ -1194,13 +1113,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>Critic 在提升 RAG 系统可靠性方面分别采用了什么核心方法？</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>MAIN</t>
+      <t>solving tools, along with a knowledge</t>
     </r>
     <r>
       <rPr>
@@ -1220,7 +1133,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>RAG 采用多智能体协作过滤机制，通过三个 LLM 智能体（Predictor、Judge、Final</t>
+      <t>graph agent, called Mind</t>
     </r>
     <r>
       <rPr>
@@ -1240,15 +1153,15 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>Predictor）对检索文档进行相关性评分和排序，并利用自适应阈值动态过滤噪声文档，无需训练。
-RAG</t>
+      <t>Map, to serve as memory."
+"In this paper, we propose AR-MCTS, a universal framework designed to progressively improve the reasoning capabilities of MLLMs through Active Retrieval (AR) and Monte Carlo Tree Search (MCTS). AR-MCTS follows the MCTS algorithm and heuristically integrates an active retrieval mechanism during the expansion stage to automatically acquire high</t>
     </r>
     <r>
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Cambria Math"/>
-        <family val="2"/>
+        <family val="1"/>
         <charset val="1"/>
       </rPr>
       <t>‑</t>
@@ -1258,40 +1171,164 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="等线"/>
-        <family val="2"/>
+        <family val="3"/>
+        <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
-      <t>Critic 采用批评引导的智能体工作流，首先构建层次化 RAG 错误系统（3 级错误类型，含 4000+ 细粒度标签），然后训练轻量级错误批评模型进行自动错误诊断，最后通过规划智能体根据错误反馈定制并执行修正方案。</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>“To address these challenges, we propose MultiAgent Filtering Retrieval-Augmented Generation (MAIN-RAG), a novel training-free framework designed to enhance the performance and reliability of RAG systems. Unlike existing methods that often rely on computationally intensive training or fine-tuning, MAIN-RAG leverages a collaborative multi-agent approach where multiple LLM agents filter and score retrieved documents. This consensus-driven strategy ensures that only the most relevant and high-quality documents are utilized for generation, significantly reducing noise without sacrificing recall.”
-“The proposed framework MAIN-RAG is to identify noisy retrieved documents for filtering out, consisting of three LLM agents: Agent-1 (Predictor), Agent-2 (Judge), and Agent-3 (Final-Predictor).”
-“We propose RAG-Critic, a novel framework that leverages a critic-guided agentic workflow to improve RAG capabilities autonomously. Specifically, we initially design a data-driven error mining pipeline to establish a hierarchical RAG error system. Based on this system, we progressively align an error-critic model using a coarse-to-fine training objective, which automatically provides fine-grained error feedback. Finally, we design a critic-guided agentic RAG workflow that customizes executor-based solution flows based on the error-critic model’s feedback, facilitating an error-driven self-correction process.”
-"In this paper, we introduce RAG-Critic, a novel framework that utilizes a critic-guided agentic workflow to autonomously enhance RAG capabilities. We first design a data-driven error mining pipeline to establish a hierarchical RAG error system. Using this system, we progressively align an error-critic model with a coarse-to-fine training objective, automating the fine-grained error feedback. We then introduce the critic-guided agentic workflow, which facilitates an error-driven correction by autonomously customizing executor-based solution flows based on error feedback."</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>2025.acl-long.131_MAIN-RAG.pdf 第1页, 第3页
-2025.acl-long.179_RAG-Critic.pdf 第1页, 第9页</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>"Results in Figure 7 show that the machine and human evaluations show a high degree of alignment in all metrics. The final absolute difference between the human evaluation and the machine evaluation is 1.67%."
-"Furthermore, the use of LLMs for scoring the proposed metrics demonstrates a high level of consistency with human evaluations."</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>2025.acl-long.418_RAGEval.pdf, 第11页, 第1页</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>RAG噪声被分为有益噪声和有害噪声。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>在SafeRAG中"silver noise"的定义是什么？</t>
+      <t>quality step</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Cambria Math"/>
+        <family val="1"/>
+        <charset val="1"/>
+      </rPr>
+      <t>‑</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>wise reasoning annotations."
+"We propose AR</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Cambria Math"/>
+        <family val="1"/>
+        <charset val="1"/>
+      </rPr>
+      <t>‑</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>MCTS, a universal framework dedicated to progressively improving the complex reasoning capabilities of MLLMs through Active Retrieval and Monte Carlo Tree Search."</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+"We introduced Agentic Reasoning, a framework that enhances LLM reasoning by integrating MindMap, web search, and coding."</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Agentic Reasoning - 2025.acl-long.1383.pdf , 第1页, 第2页；AR-MCTS - 2025.acl-long.180.pdf , 第1页, 第2页,  第8页</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2025.acl-long.1476_Astute RAG, 第2页,第5页,</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>“However, the inherent gap between user queries and relevant documents hinders precise matching. We introduce QAEncoder, a training</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Cambria Math"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t>‑</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>free approach to bridge this gap.”
+"Despite advancements, a significant challenge that persists is bridging the gap between user queries and documents across lexical, syntactic, semantic, and content dimensions(Zheng et al., 2020;Nogueira et al., 2019; Cheriton, 2019),termed the document-query gap."
+"In this paper, we propose QAEncoder to bridge the document query gap from the query-centric perspective—a novel, training-free, and pioneering approach. QAEncoder replaces document embeddings with the expectation of query embeddings, theoretically supported by the conical distribution hypothesis and practically enhanced by document fingerprint strategies."
+“However, LLMs sometimes produce false or misleading responses, also known as hallucinations. Therefore, grounding the generated answers in contextually provided information i.e., providing evidence for the generated text is paramount for LLMs' trustworthiness. Providing this information is the task of context attribution.”
+“This poses the need for context attribution methods that create links between the answer and different relevant parts of the (potentially large) reference text.”
+"We investigated the task of context attribution in QA. We focused on approaches that enhance attribution performance without relying on prohibitive human annotations. Our proposed data synthesis strategy, SYNQA, enables the generation of high-quality synthetic attribution data, leading to substantial improvements in fine-tuned small models."</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2025.acl-long.217_QAEncoder.pdf, 第1页, 第1页, 第9页; 2025.acl-long.828_On Synthesizing Data for Context Attribution in Question Answering, 第1页, 第1页, 第9页</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>"To render LLMs resilient to imperfect retrieval, we propose ASTUTE RAG, a novel RAG approach that adaptively elicits essential information from LLMs' internal knowledge, iteratively consolidates internal and external knowledge with source-awareness, and finalizes the answer according to information reliability."
+“We propose ASTUTE RAG, which explicitly analyzes LLM-internal and external knowledge in-context, assesses their reliability, and recovers from RAG failures with black-box access.”
+“ASTUTE RAG is designed to better leverage collective knowledge from both internal knowledge of LLMs and external corpus, for more reliable responses.”
+"Our objective is to mitigate the effects of imperfect retrieval augmentation, resolve knowledge conflicts between the LLM's internal knowledge and external sources (such as custom/public corpora and knowledge bases), and ultimately produce more accurate and reliable responses from LLMs."</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2025.acl-long.1476_Astute RAG.pdf, 第1页, 第二页, 第五页, 第4页</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>论文 2025.acl-long.861.pdf（SETR），第3页, 第4页</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>"We introduce QAEncoder, a training-free approach to bridge this gap. Specifically, QAEncoder estimates the expectation of potential queries in the embedding space as a robust surrogate for the document embedding, and attaches document fingerprints to effectively distinguish these embeddings. ."
+"QAEncoder addresses the document-query gap by generating a diverse set of queries for each document to create semantically aligned embeddings. Additionally, document fingerprint strategies are employed to ensure document distinguishability."</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2025.acl-long.217.pdf (第1页), 第5页</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>"In contrast, RankCoT demonstrates a 2.5% improvement over vanilla RAG model, indicating its effectiveness in providing more meaningful refinements that help LLMs better answer questions."
+"In the Miss-Answer scenario, the performance of vanilla RAG models significantly drops compared to LLMs w/o RAG, indicating that query-irrelevant documents mislead LLMs into producing incorrect answers."</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>论文 2025.acl-long.629.pdf（RankCoT），第6页, 第7页, 第12页有表格</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2025.acl-long.1178.pdf (第7页, 第15页, 第6页)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>"FaithfulRAG adopts a novel self-fact mining module to externalize the LLM’s understanding of the question, obtaining fine-grained knowledge at the fact level."
+"We propose a novel faithful framework (Faithful RAG) that explicitly identifies and resolves knowledge conflicts at the fact level. Faithful RAG first concretizes the model's parametric knowledge at the fact level and then identifies conflicting knowledge by aligning self-fact with contexts. After that, Faithful RAG designs a self-think module, allowing LLMs to reason about and integrate conflicting facts before generation."
+"To render LLMs resilient to imperfect retrieval, we propose ASTUTE RAG, a novel RAG approach that adaptively elicits essential information from LLMs' internal knowledge, iteratively consolidates internal and external knowledge with source-awareness, and finalizes the answer according to information reliability."
+"Moreover, we allow the LLM to perform adaptive generation of passages in its internal knowledge. The LLM can decide how many passages to generate by itself."
+"We first provide an overview of ASTUTE RAG(Sec. 4.1). Subsequently, we delve into the three major steps of ASTUTE RAG, including adaptive generation of internal knowledge (Sec. 4.2), source aware knowledge consolidation (Sec. 4.3), and answer finalization (Sec. 4.4)."
+"To address this, we introduce ASTUTE RAG, a novel approach that leverages the internal knowledge of LLMs and iteratively refines the generated responses by consolidating internal and external knowledge in a source-aware way. We demonstrate the effectiveness of ASTUTE RAG in mitigating the negative effects of imperfect retrieval and improving the robustness of RAG, particularly in challenging scenarios with unreliable external sources."</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>《FaithfulRAG》,第2页
+《FaithfulRAG》,第9页
+《Astute RAG》, 第1页
+《Astute RAG》, 第5页
+《Astute RAG》, 第4页
+《Astute RAG》, 第9页</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1685,44 +1722,44 @@
     </row>
     <row r="2" spans="1:4" ht="168" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
-        <v>87</v>
+        <v>75</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>139</v>
+        <v>113</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>92</v>
+        <v>80</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="98" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
-        <v>182</v>
+        <v>150</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>88</v>
+        <v>76</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>91</v>
+        <v>79</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="308" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>181</v>
+        <v>149</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>143</v>
+        <v>117</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>144</v>
+        <v>118</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="350" x14ac:dyDescent="0.3">
@@ -1730,125 +1767,125 @@
         <v>16</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>145</v>
+        <v>119</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>146</v>
+        <v>120</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="280" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
-        <v>138</v>
+        <v>112</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>151</v>
+        <v>125</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>147</v>
+        <v>121</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="364" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>152</v>
+        <v>126</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>96</v>
+        <v>84</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="84" x14ac:dyDescent="0.3">
       <c r="A8" s="3" t="s">
-        <v>69</v>
+        <v>58</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>97</v>
+        <v>85</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>98</v>
+        <v>86</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="378" x14ac:dyDescent="0.3">
       <c r="A9" s="3" t="s">
-        <v>172</v>
+        <v>140</v>
       </c>
       <c r="B9" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" ht="294" x14ac:dyDescent="0.3">
+      <c r="A10" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>173</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" ht="364" x14ac:dyDescent="0.3">
+      <c r="A11" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="D11" s="4" t="s">
         <v>159</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>99</v>
-      </c>
-      <c r="D9" s="3" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" ht="210" x14ac:dyDescent="0.3">
-      <c r="A10" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="B10" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="C10" s="3" t="s">
-        <v>101</v>
-      </c>
-      <c r="D10" s="3" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" ht="224" x14ac:dyDescent="0.3">
-      <c r="A11" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="B11" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="C11" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="D11" s="4" t="s">
-        <v>54</v>
       </c>
     </row>
     <row r="12" spans="1:4" ht="126" x14ac:dyDescent="0.3">
       <c r="A12" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B12" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="B12" s="1" t="s">
-        <v>24</v>
-      </c>
       <c r="C12" s="1" t="s">
-        <v>104</v>
+        <v>89</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>105</v>
+        <v>90</v>
       </c>
     </row>
     <row r="13" spans="1:4" ht="409.5" x14ac:dyDescent="0.3">
       <c r="A13" s="1" t="s">
-        <v>85</v>
+        <v>73</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>106</v>
+        <v>91</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>107</v>
+        <v>92</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>108</v>
+        <v>93</v>
       </c>
     </row>
   </sheetData>
@@ -1885,16 +1922,16 @@
     </row>
     <row r="2" spans="1:4" ht="168" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
-        <v>44</v>
+        <v>152</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>45</v>
+        <v>153</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>174</v>
+        <v>142</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>160</v>
+        <v>133</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="182" x14ac:dyDescent="0.3">
@@ -1902,27 +1939,27 @@
         <v>3</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>109</v>
+        <v>94</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" ht="168" x14ac:dyDescent="0.3">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" ht="210" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
-        <v>161</v>
+        <v>134</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>164</v>
+        <v>135</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="392" x14ac:dyDescent="0.3">
@@ -1930,111 +1967,111 @@
         <v>14</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>111</v>
+        <v>95</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>112</v>
+        <v>96</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="98" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
-        <v>165</v>
+        <v>151</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>72</v>
+        <v>61</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>113</v>
+        <v>97</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>114</v>
+        <v>98</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="154" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
-        <v>73</v>
+        <v>62</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>74</v>
+        <v>63</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>75</v>
+        <v>64</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>76</v>
+        <v>175</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="126" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="C8" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="B8" s="1" t="s">
-        <v>149</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>30</v>
-      </c>
       <c r="D8" s="1" t="s">
-        <v>67</v>
+        <v>56</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="112" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
-        <v>77</v>
+        <v>65</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>78</v>
+        <v>66</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>115</v>
+        <v>99</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>116</v>
+        <v>100</v>
       </c>
     </row>
     <row r="10" spans="1:4" ht="210" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="B10" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="B10" s="1" t="s">
+      <c r="C10" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="C10" s="1" t="s">
-        <v>40</v>
-      </c>
       <c r="D10" s="1" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" ht="154" x14ac:dyDescent="0.3">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" ht="196" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="s">
-        <v>117</v>
+        <v>101</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>118</v>
+        <v>102</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>64</v>
+        <v>176</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>49</v>
+        <v>177</v>
       </c>
     </row>
     <row r="12" spans="1:4" ht="84" x14ac:dyDescent="0.3">
       <c r="A12" s="1" t="s">
-        <v>166</v>
+        <v>136</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>169</v>
+        <v>139</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>167</v>
+        <v>137</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>168</v>
+        <v>138</v>
       </c>
     </row>
   </sheetData>
@@ -2078,7 +2115,7 @@
         <v>6</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>119</v>
+        <v>154</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="56" x14ac:dyDescent="0.3">
@@ -2092,133 +2129,133 @@
         <v>10</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" ht="70" x14ac:dyDescent="0.3">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" ht="140" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
-        <v>141</v>
+        <v>115</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>142</v>
+        <v>116</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>51</v>
+        <v>178</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" ht="70" x14ac:dyDescent="0.3">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" ht="140" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
-        <v>79</v>
+        <v>67</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>80</v>
+        <v>68</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>20</v>
+        <v>155</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" ht="126" x14ac:dyDescent="0.3">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" ht="182" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B6" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="B6" s="1" t="s">
-        <v>26</v>
-      </c>
       <c r="C6" s="1" t="s">
-        <v>120</v>
+        <v>162</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>121</v>
+        <v>161</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="140" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
-        <v>123</v>
+        <v>104</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>124</v>
+        <v>105</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>122</v>
+        <v>103</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>56</v>
+        <v>48</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="70" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
-        <v>148</v>
+        <v>122</v>
       </c>
       <c r="B8" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C8" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="C8" s="1" t="s">
-        <v>34</v>
-      </c>
       <c r="D8" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="112" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>125</v>
+        <v>106</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>57</v>
+        <v>49</v>
       </c>
     </row>
     <row r="10" spans="1:4" ht="409.5" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B10" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="B10" s="1" t="s">
-        <v>37</v>
-      </c>
       <c r="C10" s="1" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" ht="168" x14ac:dyDescent="0.3">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" ht="266" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="s">
-        <v>59</v>
+        <v>51</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>65</v>
+        <v>157</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>60</v>
+        <v>158</v>
       </c>
     </row>
     <row r="12" spans="1:4" ht="112" x14ac:dyDescent="0.3">
       <c r="A12" s="1" t="s">
-        <v>173</v>
+        <v>141</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>158</v>
+        <v>131</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>179</v>
+        <v>147</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>180</v>
+        <v>148</v>
       </c>
     </row>
   </sheetData>
@@ -2251,18 +2288,18 @@
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:4" ht="266" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:4" ht="409.5" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
-        <v>81</v>
+        <v>69</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>126</v>
+        <v>107</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>127</v>
+        <v>181</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>128</v>
+        <v>182</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="409.5" x14ac:dyDescent="0.3">
@@ -2270,13 +2307,13 @@
         <v>7</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>129</v>
+        <v>108</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>130</v>
+        <v>163</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>131</v>
+        <v>164</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="196" x14ac:dyDescent="0.3">
@@ -2284,83 +2321,83 @@
         <v>17</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>61</v>
+        <v>52</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>132</v>
+        <v>109</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>150</v>
+        <v>124</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="196" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
-        <v>153</v>
+        <v>127</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>154</v>
+        <v>128</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>133</v>
+        <v>110</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>134</v>
+        <v>111</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="154" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
-        <v>82</v>
+        <v>70</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>84</v>
+        <v>72</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>62</v>
+        <v>53</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="409.5" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
-        <v>155</v>
+        <v>129</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>156</v>
+        <v>130</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>157</v>
+        <v>168</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>135</v>
+        <v>169</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="409.5" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
-        <v>175</v>
+        <v>143</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>176</v>
+        <v>144</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>177</v>
+        <v>145</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" ht="365.5" x14ac:dyDescent="0.3">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" ht="409.5" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
-        <v>86</v>
+        <v>74</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>83</v>
+        <v>71</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>136</v>
+        <v>171</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>137</v>
+        <v>172</v>
       </c>
     </row>
   </sheetData>
@@ -2397,7 +2434,7 @@
         <v>11</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>68</v>
+        <v>57</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>19</v>
@@ -2411,7 +2448,7 @@
         <v>12</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>68</v>
+        <v>57</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>19</v>
@@ -2422,10 +2459,10 @@
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
-        <v>140</v>
+        <v>114</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>68</v>
+        <v>57</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>19</v>
@@ -2439,7 +2476,7 @@
         <v>18</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>68</v>
+        <v>57</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>19</v>
@@ -2450,10 +2487,10 @@
     </row>
     <row r="6" spans="1:4" ht="28" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>68</v>
+        <v>57</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>19</v>
@@ -2464,10 +2501,10 @@
     </row>
     <row r="7" spans="1:4" ht="28" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>68</v>
+        <v>57</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>19</v>
@@ -2478,10 +2515,10 @@
     </row>
     <row r="8" spans="1:4" ht="28" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>68</v>
+        <v>57</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>19</v>
@@ -2492,10 +2529,10 @@
     </row>
     <row r="9" spans="1:4" ht="28" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>68</v>
+        <v>57</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>19</v>

--- a/code/测试集.xlsx
+++ b/code/测试集.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\rag_project\code\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{926AFFCC-1877-4B84-A7BB-EAD412D37C35}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A1C0FDFE-BF2B-46E5-A9EF-13C24049957A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="12710" yWindow="0" windowWidth="12980" windowHeight="13770" firstSheet="1" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="12710" yWindow="0" windowWidth="12980" windowHeight="13770" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="定义类" sheetId="1" r:id="rId1"/>
@@ -255,11 +255,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>LongBench v2: 2025.acl-long.183.pdf，第1页
-AGENTGYM: 2025.acl-long.1355.pdf, 第1页</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>RAG噪声被分为哪两类？</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -338,11 +333,6 @@
 核心痛点：用户的自然语言查询与知识库中的文档之间存在语义和词汇上的鸿沟，导致检索模块无法精准召回相关文档。
 《On Synthesizing Data for Context Attribution... (SYNQA)》侧重于“生成后阶段”
 核心痛点：大语言模型在生成答案时容易产生幻觉，用户很难验证生成的答案是否真的基于提供的上下文，缺乏可解释性和事实依据。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve"> "LongBench v2 consists of 503 challenging multiple-choice questions, with contexts ranging from 8k to 2M words, across six major task categories."
- "However, the community lacks a unified interactive framework that covers diverse environments for comprehensive evaluation of agents, and enables exploration and learning for their self-improvement. To address this, we propose AGENTGYM, a framework featuring 7 real-world scenarios, 14 environments, and 89 tasks for unified, real-time, and concurrent agent interaction."</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -446,12 +436,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t xml:space="preserve">"ASTUTE RAG first adaptively elicits LLMs' knowledge and then conducts source-aware knowledge consolidation. The desiderata is combining consistent information, identifying conflicting information, and filtering out irrelevant information."
-“To consolidate knowledge, we prompt the LLM (with pcon in Appx. A) to identify consistent information across passages, detect conflicting information between each group of consistent passages, and filter out irrelevant information.”
-</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>“Another key advantage of our framework is its potential for privacy protection. Typically, when querying large- scale LLMs, local deployment is not feasible, requiring users to upload their private queries to cloud- based LLMs, raising privacy concerns. Our framework addresses this issue by enabling local SLMs to leverage the knowledge of large models while preserving user privacy."
 "With our approach, the local model first reformulates the query (much simpler than answering the query directly), stripping any sensitive information before sending it to the cloud- based model. The cloud model then retrieves relevant evidence and knowledge graphs, which are subsequently passed back to the local model for final processing and response generation. This ensures that private data remains protected while still benefiting from the power of large- scale LLMs.”
 “2) The teacher LLM is usually heavy in size and deployed on the cloud, and the student is on local devices, it is simple to develop methods for preserving privacy using our proposed framework by transmitting only de- identified queries and structured knowledge instead of full responses, as we have introduced in Section 3.3.”</t>
@@ -1071,174 +1055,7 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <r>
-      <t xml:space="preserve"> "Agentic Reasoning dynamically leverages web search, code execution, and structured memory to address complex problems requiring deep research. A key innovation in our framework is the Mind-Map agent, which constructs a structured knowledge graph to store reasoning context and track logical relationships."
-"In the overall process, we deploy a Web</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Cambria Math"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t>‑</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="等线"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Search agent and a Code agent as problem</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Cambria Math"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t>‑</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="等线"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>solving tools, along with a knowledge</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Cambria Math"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t>‑</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="等线"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>graph agent, called Mind</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Cambria Math"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t>‑</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="等线"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Map, to serve as memory."
-"In this paper, we propose AR-MCTS, a universal framework designed to progressively improve the reasoning capabilities of MLLMs through Active Retrieval (AR) and Monte Carlo Tree Search (MCTS). AR-MCTS follows the MCTS algorithm and heuristically integrates an active retrieval mechanism during the expansion stage to automatically acquire high</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Cambria Math"/>
-        <family val="1"/>
-        <charset val="1"/>
-      </rPr>
-      <t>‑</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="等线"/>
-        <family val="3"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>quality step</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Cambria Math"/>
-        <family val="1"/>
-        <charset val="1"/>
-      </rPr>
-      <t>‑</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="等线"/>
-        <family val="3"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>wise reasoning annotations."
-"We propose AR</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Cambria Math"/>
-        <family val="1"/>
-        <charset val="1"/>
-      </rPr>
-      <t>‑</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="等线"/>
-        <family val="3"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>MCTS, a universal framework dedicated to progressively improving the complex reasoning capabilities of MLLMs through Active Retrieval and Monte Carlo Tree Search."</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="等线"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-"We introduced Agentic Reasoning, a framework that enhances LLM reasoning by integrating MindMap, web search, and coding."</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>Agentic Reasoning - 2025.acl-long.1383.pdf , 第1页, 第2页；AR-MCTS - 2025.acl-long.180.pdf , 第1页, 第2页,  第8页</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>2025.acl-long.1476_Astute RAG, 第2页,第5页,</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -1292,15 +1109,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>"We introduce QAEncoder, a training-free approach to bridge this gap. Specifically, QAEncoder estimates the expectation of potential queries in the embedding space as a robust surrogate for the document embedding, and attaches document fingerprints to effectively distinguish these embeddings. ."
-"QAEncoder addresses the document-query gap by generating a diverse set of queries for each document to create semantically aligned embeddings. Additionally, document fingerprint strategies are employed to ensure document distinguishability."</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>2025.acl-long.217.pdf (第1页), 第5页</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>"In contrast, RankCoT demonstrates a 2.5% improvement over vanilla RAG model, indicating its effectiveness in providing more meaningful refinements that help LLMs better answer questions."
 "In the Miss-Answer scenario, the performance of vanilla RAG models significantly drops compared to LLMs w/o RAG, indicating that query-irrelevant documents mislead LLMs into producing incorrect answers."</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -1314,8 +1122,29 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
+    <t>"ASTUTE RAG first adaptively elicits LLMs' knowledge and then conducts source-aware knowledge consolidation. The desiderata is combining consistent information, identifying conflicting information, and filtering out irrelevant information."
+“To consolidate knowledge, we prompt the LLM (with pcon in Appx. A) to identify consistent information across passages, detect conflicting information between each group of consistent passages, and filter out irrelevant information.”
+"Step 1: Consolidate information.For documents that provide consistent information, cluster them together and summarize the key details into a single, concise document.For documents with conflicting information, separate them into distinct documents, ensuring each captures the unique perspective or data.Exclude any information irrelevant to the query."</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2025.acl-long.1476_Astute RAG, 第2页,第5页,第16页</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>"We introduce QAEncoder, a training-free approach to bridge this gap. Specifically, QAEncoder estimates the expectation of potential queries in the embedding space as a robust surrogate for the document embedding, and attaches document fingerprints to effectively distinguish these embeddings. ."
+"QAEncoder addresses the document-query gap by generating a diverse set of queries for each document to create semantically aligned embeddings. Additionally, document fingerprint strategies are employed to ensure document distinguishability."
+"In this paper, we propose QAEncoder to bridge the document-query gap from the query-centric perspective—a novel, training-free, and pioneering approach. QAEncoder replaces document embeddings with the expectation of query embeddings, theoretically supported by the conical distribution hypothesis and practically enhanced by document fingerprint strategies."</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2025.acl-long.217.pdf (第1页), 第5页 ,第9页</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <t>"FaithfulRAG adopts a novel self-fact mining module to externalize the LLM’s understanding of the question, obtaining fine-grained knowledge at the fact level."
 "We propose a novel faithful framework (Faithful RAG) that explicitly identifies and resolves knowledge conflicts at the fact level. Faithful RAG first concretizes the model's parametric knowledge at the fact level and then identifies conflicting knowledge by aligning self-fact with contexts. After that, Faithful RAG designs a self-think module, allowing LLMs to reason about and integrate conflicting facts before generation."
+"Our objective is to mitigate the effects of imperfect retrieval augmentation, resolve knowledge conflicts between the LLM's internal knowledge and external sources (such as custom/public corpora and knowledge bases), and ultimately produce more accurate and reliable responses from LLMs."
 "To render LLMs resilient to imperfect retrieval, we propose ASTUTE RAG, a novel RAG approach that adaptively elicits essential information from LLMs' internal knowledge, iteratively consolidates internal and external knowledge with source-awareness, and finalizes the answer according to information reliability."
 "Moreover, we allow the LLM to perform adaptive generation of passages in its internal knowledge. The LLM can decide how many passages to generate by itself."
 "We first provide an overview of ASTUTE RAG(Sec. 4.1). Subsequently, we delve into the three major steps of ASTUTE RAG, including adaptive generation of internal knowledge (Sec. 4.2), source aware knowledge consolidation (Sec. 4.3), and answer finalization (Sec. 4.4)."
@@ -1325,10 +1154,186 @@
   <si>
     <t>《FaithfulRAG》,第2页
 《FaithfulRAG》,第9页
+《FaithfulRAG》,第4页
 《Astute RAG》, 第1页
 《Astute RAG》, 第5页
 《Astute RAG》, 第4页
 《Astute RAG》, 第9页</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve"> "LongBench v2 consists of 503 challenging multiple-choice questions, with contexts ranging from 8k to 2M words, across six major task categories."
+"Our design principle focuses on four aspects: (1) The context should be sufficiently long to cover scenarios ranging from 8k to 2M words, with a relatively even distribution across texts up to 128k words."
+ "However, the community lacks a unified interactive framework that covers diverse environments for comprehensive evaluation of agents, and enables exploration and learning for their self-improvement. To address this, we propose AGENTGYM, a framework featuring 7 real-world scenarios, 14 environments, and 89 tasks for unified, real-time, and concurrent agent interaction."
+"We adopt a hierarchical, decoupled architecture in AGENTGYM to facilitate unified, real-time, and concurrent agent-environment interactions, as illustrated in Figure 4 in Appendix B."</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>LongBench v2: 2025.acl-long.183.pdf，第1页, 第3页
+AGENTGYM: 2025.acl-long.1355.pdf, 第1页, 第4页</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve"> "Agentic Reasoning dynamically leverages web search, code execution, and structured memory to address complex problems requiring deep research. A key innovation in our framework is the Mind-Map agent, which constructs a structured knowledge graph to store reasoning context and track logical relationships."
+"In the overall process, we deploy a Web</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Cambria Math"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t>‑</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Search agent and a Code agent as problem</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Cambria Math"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t>‑</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>solving tools, along with a knowledge</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Cambria Math"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t>‑</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>graph agent, called Mind</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Cambria Math"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t>‑</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Map, to serve as memory."
+"In this paper, we propose AR-MCTS, a universal framework designed to progressively improve the reasoning capabilities of MLLMs through Active Retrieval (AR) and Monte Carlo Tree Search (MCTS). AR-MCTS follows the MCTS algorithm and heuristically integrates an active retrieval mechanism during the expansion stage to automatically acquire high</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Cambria Math"/>
+        <family val="1"/>
+        <charset val="1"/>
+      </rPr>
+      <t>‑</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>quality step</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Cambria Math"/>
+        <family val="1"/>
+        <charset val="1"/>
+      </rPr>
+      <t>‑</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>wise reasoning annotations."
+"We propose AR</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Cambria Math"/>
+        <family val="1"/>
+        <charset val="1"/>
+      </rPr>
+      <t>‑</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>MCTS, a universal framework dedicated to progressively improving the complex reasoning capabilities of MLLMs through Active Retrieval and Monte Carlo Tree Search."</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1722,44 +1727,44 @@
     </row>
     <row r="2" spans="1:4" ht="168" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="C2" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="B2" s="1" t="s">
-        <v>113</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>77</v>
-      </c>
       <c r="D2" s="1" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="98" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="B3" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="C3" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="C3" s="1" t="s">
-        <v>78</v>
-      </c>
       <c r="D3" s="1" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="308" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="350" x14ac:dyDescent="0.3">
@@ -1767,27 +1772,27 @@
         <v>16</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="280" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="364" x14ac:dyDescent="0.3">
@@ -1795,55 +1800,55 @@
         <v>21</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="84" x14ac:dyDescent="0.3">
       <c r="A8" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B8" s="3" t="s">
         <v>30</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="378" x14ac:dyDescent="0.3">
       <c r="A9" s="3" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
     </row>
     <row r="10" spans="1:4" ht="294" x14ac:dyDescent="0.3">
       <c r="A10" s="3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>173</v>
+        <v>168</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>174</v>
+        <v>169</v>
       </c>
     </row>
     <row r="11" spans="1:4" ht="364" x14ac:dyDescent="0.3">
@@ -1854,10 +1859,10 @@
         <v>47</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
     </row>
     <row r="12" spans="1:4" ht="126" x14ac:dyDescent="0.3">
@@ -1868,24 +1873,24 @@
         <v>23</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
     </row>
     <row r="13" spans="1:4" ht="409.5" x14ac:dyDescent="0.3">
       <c r="A13" s="1" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="B13" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="D13" s="1" t="s">
         <v>91</v>
-      </c>
-      <c r="C13" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="D13" s="1" t="s">
-        <v>93</v>
       </c>
     </row>
   </sheetData>
@@ -1922,44 +1927,44 @@
     </row>
     <row r="2" spans="1:4" ht="168" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" ht="182" x14ac:dyDescent="0.3">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" ht="294" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>3</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>94</v>
+        <v>174</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>170</v>
+        <v>175</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="210" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="392" x14ac:dyDescent="0.3">
@@ -1970,38 +1975,38 @@
         <v>44</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="98" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="154" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="B7" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="B7" s="1" t="s">
+      <c r="C7" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="C7" s="1" t="s">
-        <v>64</v>
-      </c>
       <c r="D7" s="1" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="126" x14ac:dyDescent="0.3">
@@ -2009,27 +2014,27 @@
         <v>28</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>29</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="112" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="B9" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="B9" s="1" t="s">
-        <v>66</v>
-      </c>
       <c r="C9" s="1" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
     </row>
     <row r="10" spans="1:4" ht="210" x14ac:dyDescent="0.3">
@@ -2046,12 +2051,12 @@
         <v>45</v>
       </c>
     </row>
-    <row r="11" spans="1:4" ht="196" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:4" ht="336" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>176</v>
@@ -2062,16 +2067,16 @@
     </row>
     <row r="12" spans="1:4" ht="84" x14ac:dyDescent="0.3">
       <c r="A12" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="B12" s="1" t="s">
         <v>136</v>
       </c>
-      <c r="B12" s="1" t="s">
-        <v>139</v>
-      </c>
       <c r="C12" s="1" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
     </row>
   </sheetData>
@@ -2115,7 +2120,7 @@
         <v>6</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="56" x14ac:dyDescent="0.3">
@@ -2134,30 +2139,30 @@
     </row>
     <row r="4" spans="1:4" ht="140" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>178</v>
+        <v>171</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>179</v>
+        <v>172</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="140" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="B5" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="B5" s="1" t="s">
-        <v>68</v>
-      </c>
       <c r="C5" s="1" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="182" x14ac:dyDescent="0.3">
@@ -2168,21 +2173,21 @@
         <v>25</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="140" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="D7" s="1" t="s">
         <v>48</v>
@@ -2190,7 +2195,7 @@
     </row>
     <row r="8" spans="1:4" ht="70" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>32</v>
@@ -2210,7 +2215,7 @@
         <v>50</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="D9" s="1" t="s">
         <v>49</v>
@@ -2224,10 +2229,10 @@
         <v>36</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>180</v>
+        <v>173</v>
       </c>
     </row>
     <row r="11" spans="1:4" ht="266" x14ac:dyDescent="0.3">
@@ -2238,24 +2243,24 @@
         <v>40</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
     </row>
     <row r="12" spans="1:4" ht="112" x14ac:dyDescent="0.3">
       <c r="A12" s="1" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
     </row>
   </sheetData>
@@ -2290,16 +2295,16 @@
     </row>
     <row r="2" spans="1:4" ht="409.5" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="409.5" x14ac:dyDescent="0.3">
@@ -2307,13 +2312,13 @@
         <v>7</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="196" x14ac:dyDescent="0.3">
@@ -2324,80 +2329,80 @@
         <v>52</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="196" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" ht="154" x14ac:dyDescent="0.3">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" ht="266" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>26</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>72</v>
+        <v>180</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>53</v>
+        <v>181</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="409.5" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>168</v>
+        <v>182</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="409.5" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="D8" s="1" t="s">
         <v>143</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>144</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>145</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>146</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="409.5" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>171</v>
+        <v>166</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>172</v>
+        <v>167</v>
       </c>
     </row>
   </sheetData>
@@ -2434,7 +2439,7 @@
         <v>11</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>19</v>
@@ -2448,7 +2453,7 @@
         <v>12</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>19</v>
@@ -2459,10 +2464,10 @@
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>19</v>
@@ -2476,7 +2481,7 @@
         <v>18</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>19</v>
@@ -2490,7 +2495,7 @@
         <v>20</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>19</v>
@@ -2504,7 +2509,7 @@
         <v>27</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>19</v>
@@ -2518,7 +2523,7 @@
         <v>41</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>19</v>
@@ -2532,7 +2537,7 @@
         <v>42</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>19</v>

--- a/code/测试集.xlsx
+++ b/code/测试集.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\rag_project\code\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A1C0FDFE-BF2B-46E5-A9EF-13C24049957A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{09F18486-EAE6-4B39-8A82-EFDD551615E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="12710" yWindow="0" windowWidth="12980" windowHeight="13770" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="定义类" sheetId="1" r:id="rId1"/>

--- a/code/测试集.xlsx
+++ b/code/测试集.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\rag_project\code\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{09F18486-EAE6-4B39-8A82-EFDD551615E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D28E72F4-3D56-4E34-B8F4-EF5C179BDB2B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="定义类" sheetId="1" r:id="rId1"/>
@@ -305,10 +305,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>CypherBench 是如何从 RDF 图生成领域特定属性图的？</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>CypherBench 通过将 RDF 图转换为多个领域特定的属性图（domain-specific property graphs）来实现这一过程，并使用 Cypher 语言对其进行查询。</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1334,6 +1330,10 @@
       <t xml:space="preserve">
 </t>
     </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>CypherBench 提出了什么核心方法来应对 RDF 查询的挑战？</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1727,30 +1727,30 @@
     </row>
     <row r="2" spans="1:4" ht="168" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="98" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C3" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="D3" s="1" t="s">
         <v>76</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>77</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="308" x14ac:dyDescent="0.3">
@@ -1758,13 +1758,13 @@
         <v>53</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C4" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="D4" s="1" t="s">
         <v>114</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>115</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="350" x14ac:dyDescent="0.3">
@@ -1772,27 +1772,27 @@
         <v>16</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C5" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="D5" s="1" t="s">
         <v>116</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>117</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="280" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="364" x14ac:dyDescent="0.3">
@@ -1800,13 +1800,13 @@
         <v>21</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C7" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="D7" s="1" t="s">
         <v>81</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>82</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="84" x14ac:dyDescent="0.3">
@@ -1817,24 +1817,24 @@
         <v>30</v>
       </c>
       <c r="C8" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="D8" s="3" t="s">
         <v>83</v>
-      </c>
-      <c r="D8" s="3" t="s">
-        <v>84</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="378" x14ac:dyDescent="0.3">
       <c r="A9" s="3" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C9" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="D9" s="3" t="s">
         <v>85</v>
-      </c>
-      <c r="D9" s="3" t="s">
-        <v>86</v>
       </c>
     </row>
     <row r="10" spans="1:4" ht="294" x14ac:dyDescent="0.3">
@@ -1845,10 +1845,10 @@
         <v>58</v>
       </c>
       <c r="C10" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="D10" s="3" t="s">
         <v>168</v>
-      </c>
-      <c r="D10" s="3" t="s">
-        <v>169</v>
       </c>
     </row>
     <row r="11" spans="1:4" ht="364" x14ac:dyDescent="0.3">
@@ -1859,10 +1859,10 @@
         <v>47</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="12" spans="1:4" ht="126" x14ac:dyDescent="0.3">
@@ -1873,24 +1873,24 @@
         <v>23</v>
       </c>
       <c r="C12" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="D12" s="1" t="s">
         <v>87</v>
-      </c>
-      <c r="D12" s="1" t="s">
-        <v>88</v>
       </c>
     </row>
     <row r="13" spans="1:4" ht="409.5" x14ac:dyDescent="0.3">
       <c r="A13" s="1" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B13" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="C13" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="C13" s="1" t="s">
+      <c r="D13" s="1" t="s">
         <v>90</v>
-      </c>
-      <c r="D13" s="1" t="s">
-        <v>91</v>
       </c>
     </row>
   </sheetData>
@@ -1927,16 +1927,16 @@
     </row>
     <row r="2" spans="1:4" ht="168" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="B2" s="1" t="s">
         <v>149</v>
       </c>
-      <c r="B2" s="1" t="s">
-        <v>150</v>
-      </c>
       <c r="C2" s="1" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="294" x14ac:dyDescent="0.3">
@@ -1947,24 +1947,24 @@
         <v>54</v>
       </c>
       <c r="C3" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="D3" s="1" t="s">
         <v>174</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>175</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="210" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="B4" s="1" t="s">
         <v>131</v>
       </c>
-      <c r="B4" s="1" t="s">
-        <v>132</v>
-      </c>
       <c r="C4" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="D4" s="1" t="s">
         <v>162</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>163</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="392" x14ac:dyDescent="0.3">
@@ -1975,24 +1975,24 @@
         <v>44</v>
       </c>
       <c r="C5" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="D5" s="1" t="s">
         <v>92</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>93</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="98" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>60</v>
       </c>
       <c r="C6" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="D6" s="1" t="s">
         <v>94</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>95</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="154" x14ac:dyDescent="0.3">
@@ -2006,7 +2006,7 @@
         <v>63</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="126" x14ac:dyDescent="0.3">
@@ -2014,7 +2014,7 @@
         <v>28</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>29</v>
@@ -2025,16 +2025,16 @@
     </row>
     <row r="9" spans="1:4" ht="112" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="B9" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="B9" s="1" t="s">
-        <v>65</v>
-      </c>
       <c r="C9" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="D9" s="1" t="s">
         <v>96</v>
-      </c>
-      <c r="D9" s="1" t="s">
-        <v>97</v>
       </c>
     </row>
     <row r="10" spans="1:4" ht="210" x14ac:dyDescent="0.3">
@@ -2053,30 +2053,30 @@
     </row>
     <row r="11" spans="1:4" ht="336" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="B11" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="B11" s="1" t="s">
-        <v>99</v>
-      </c>
       <c r="C11" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="D11" s="1" t="s">
         <v>176</v>
-      </c>
-      <c r="D11" s="1" t="s">
-        <v>177</v>
       </c>
     </row>
     <row r="12" spans="1:4" ht="84" x14ac:dyDescent="0.3">
       <c r="A12" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="C12" s="1" t="s">
         <v>133</v>
       </c>
-      <c r="B12" s="1" t="s">
-        <v>136</v>
-      </c>
-      <c r="C12" s="1" t="s">
+      <c r="D12" s="1" t="s">
         <v>134</v>
-      </c>
-      <c r="D12" s="1" t="s">
-        <v>135</v>
       </c>
     </row>
   </sheetData>
@@ -2120,7 +2120,7 @@
         <v>6</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="56" x14ac:dyDescent="0.3">
@@ -2139,30 +2139,30 @@
     </row>
     <row r="4" spans="1:4" ht="140" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="B4" s="1" t="s">
         <v>112</v>
       </c>
-      <c r="B4" s="1" t="s">
-        <v>113</v>
-      </c>
       <c r="C4" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="D4" s="1" t="s">
         <v>171</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>172</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="140" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="B5" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="B5" s="1" t="s">
-        <v>67</v>
-      </c>
       <c r="C5" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="D5" s="1" t="s">
         <v>152</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>153</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="182" x14ac:dyDescent="0.3">
@@ -2173,21 +2173,21 @@
         <v>25</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="140" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="B7" s="1" t="s">
         <v>101</v>
       </c>
-      <c r="B7" s="1" t="s">
-        <v>102</v>
-      </c>
       <c r="C7" s="1" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D7" s="1" t="s">
         <v>48</v>
@@ -2195,7 +2195,7 @@
     </row>
     <row r="8" spans="1:4" ht="70" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>32</v>
@@ -2215,7 +2215,7 @@
         <v>50</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D9" s="1" t="s">
         <v>49</v>
@@ -2229,10 +2229,10 @@
         <v>36</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="11" spans="1:4" ht="266" x14ac:dyDescent="0.3">
@@ -2243,24 +2243,24 @@
         <v>40</v>
       </c>
       <c r="C11" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="D11" s="1" t="s">
         <v>154</v>
-      </c>
-      <c r="D11" s="1" t="s">
-        <v>155</v>
       </c>
     </row>
     <row r="12" spans="1:4" ht="112" x14ac:dyDescent="0.3">
       <c r="A12" s="1" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C12" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="D12" s="1" t="s">
         <v>144</v>
-      </c>
-      <c r="D12" s="1" t="s">
-        <v>145</v>
       </c>
     </row>
   </sheetData>
@@ -2295,16 +2295,16 @@
     </row>
     <row r="2" spans="1:4" ht="409.5" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C2" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="D2" s="1" t="s">
         <v>178</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>179</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="409.5" x14ac:dyDescent="0.3">
@@ -2312,13 +2312,13 @@
         <v>7</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C3" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="D3" s="1" t="s">
         <v>160</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>161</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="196" x14ac:dyDescent="0.3">
@@ -2329,80 +2329,80 @@
         <v>52</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="196" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="B5" s="1" t="s">
         <v>124</v>
       </c>
-      <c r="B5" s="1" t="s">
-        <v>125</v>
-      </c>
       <c r="C5" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="D5" s="1" t="s">
         <v>107</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>108</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="266" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>26</v>
       </c>
       <c r="C6" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="D6" s="1" t="s">
         <v>180</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>181</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="409.5" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="B7" s="1" t="s">
         <v>126</v>
       </c>
-      <c r="B7" s="1" t="s">
-        <v>127</v>
-      </c>
       <c r="C7" s="1" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="409.5" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="B8" s="1" t="s">
         <v>140</v>
       </c>
-      <c r="B8" s="1" t="s">
+      <c r="C8" s="1" t="s">
         <v>141</v>
       </c>
-      <c r="C8" s="1" t="s">
+      <c r="D8" s="1" t="s">
         <v>142</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>143</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="409.5" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C9" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="D9" s="1" t="s">
         <v>166</v>
-      </c>
-      <c r="D9" s="1" t="s">
-        <v>167</v>
       </c>
     </row>
   </sheetData>
@@ -2464,7 +2464,7 @@
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>56</v>

--- a/code/测试集.xlsx
+++ b/code/测试集.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\rag_project\code\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D28E72F4-3D56-4E34-B8F4-EF5C179BDB2B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0AE1D14F-C5BD-4694-AFCC-B0E6F0272F3F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="定义类" sheetId="1" r:id="rId1"/>
